--- a/tame_output/ON/bt/strategyON_20240624.xlsx
+++ b/tame_output/ON/bt/strategyON_20240624.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.7%</t>
+          <t>-70.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>460.9%</t>
+          <t>460.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-548.4%</t>
+          <t>-549.7%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>121.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-179.6%</t>
+          <t>-180.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-188.9%</t>
+          <t>-172.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-197.2%</t>
+          <t>-204.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-83.0%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.207052935372154</v>
+        <v>-8.380163133751857</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1660154436400161</v>
+        <v>-0.2352595229918975</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.595970334090773</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.15957995436813</v>
+        <v>2.094077642739804</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.393772643681457</v>
+        <v>-8.56688284206116</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2447296314981404</v>
+        <v>-0.3139737108500213</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.595970334090773</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.155553649833727</v>
+        <v>2.0900513382054</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.776774032424088</v>
+        <v>-8.949884230803791</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3980322883167768</v>
+        <v>-0.4672763676686582</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.595970334090773</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.155451548512143</v>
+        <v>2.089949236883816</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.958643823409123</v>
+        <v>-9.131754021788826</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4682086887393604</v>
+        <v>-0.5374527680912418</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.777840125075808</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.048901189892551</v>
+        <v>1.983398878264226</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.318174145913124</v>
+        <v>-9.491284344292827</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6066705144429108</v>
+        <v>-0.6759145937947921</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.777840125075808</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.054251493190602</v>
+        <v>1.988749181562276</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.368523209367346</v>
+        <v>-9.541633407747049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6188941198674223</v>
+        <v>-0.6881381992193036</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.82818918853003</v>
+        <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.031958075075246</v>
+        <v>1.96645576344692</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.466142486788742</v>
+        <v>-9.639252685168445</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6549000802142118</v>
+        <v>-0.7241441595660931</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.925808465951427</v>
+        <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.976428259244177</v>
+        <v>1.91092594761585</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.613668574794385</v>
+        <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7110169590948967</v>
+        <v>-0.7802610384467781</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.07333455395707</v>
+        <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.890806162762363</v>
+        <v>1.825303851134037</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.817926750124249</v>
+        <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7872070321082001</v>
+        <v>-0.856451111460081</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.200973498571059</v>
+        <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.819735993112612</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.892259726384413</v>
+        <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8124576681278297</v>
+        <v>-0.8817017474797111</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.345673022505732</v>
+        <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.737398833236244</v>
+        <v>1.671896521607918</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.818789894716964</v>
+        <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7676980339674291</v>
+        <v>-0.83694211331931</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.272203190838283</v>
+        <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.796852433730135</v>
+        <v>1.731350122101808</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.993914312103508</v>
+        <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8231925801745295</v>
+        <v>-0.8924366595264104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.447327608224827</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.706333004045725</v>
+        <v>1.640830692417399</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.228366406118</v>
+        <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9241925826819215</v>
+        <v>-0.9934366620338024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.447327608224827</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.699113839144129</v>
+        <v>1.633611527515803</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.33274113714444</v>
+        <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9726146658664763</v>
+        <v>-1.041858745218357</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.551702339251273</v>
+        <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.629816809754286</v>
+        <v>1.564314498125959</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.38552729274477</v>
+        <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9926133382680504</v>
+        <v>-1.061857417619931</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.64737782583367</v>
+        <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.573527307643404</v>
+        <v>1.508024996015078</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.51156408611306</v>
+        <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.040334326986252</v>
+        <v>-1.109578406338132</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.622126203023927</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.591372009958364</v>
+        <v>1.525869698330037</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.45954857214425</v>
+        <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.015537785712326</v>
+        <v>-1.084781865064206</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.622126203023927</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.595362345644765</v>
+        <v>1.529860034016438</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.60122041386837</v>
+        <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.073681749300715</v>
+        <v>-1.142925828652596</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.622126203023927</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.593887118746023</v>
+        <v>1.528384807117697</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.55162956944353</v>
+        <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.03879200136591</v>
+        <v>-1.10803608071779</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.572535358599093</v>
+        <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.638695035565795</v>
+        <v>1.573192723937469</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.53882217643876</v>
+        <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.046720177810683</v>
+        <v>-1.115964257162564</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.621391133607994</v>
+        <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.596330436913772</v>
+        <v>1.530828125285446</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.31297702371935</v>
+        <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9468030436867099</v>
+        <v>-1.016047123038591</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.579464458020831</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.631065515302279</v>
+        <v>1.565563203673952</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.18839836738176</v>
+        <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8958324365956138</v>
+        <v>-0.9650765159474957</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.579464458020831</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.632204659858338</v>
+        <v>1.566702348230011</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.24129365542604</v>
+        <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9143567776512214</v>
+        <v>-0.9836008570031023</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.574509111932385</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.637811641673513</v>
+        <v>1.572309330045187</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.16916048013816</v>
+        <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8797698032974326</v>
+        <v>-0.9490138826493135</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.574509111932385</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.643545345912149</v>
+        <v>1.578043034283823</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.09779408752851</v>
+        <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8609605086474383</v>
+        <v>-0.9302045879993202</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.503142719322736</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.676627919084073</v>
+        <v>1.611125607455747</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.00433505354329</v>
+        <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8334603763662565</v>
+        <v>-0.9027044557181374</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.503142719322736</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.666744437771166</v>
+        <v>1.601242126142839</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.737093252674892</v>
+        <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7283982165182707</v>
+        <v>-0.7976422958701521</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.503142719322736</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.664909877271792</v>
+        <v>1.599407565643466</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.639186213998402</v>
+        <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6895357160211355</v>
+        <v>-0.7587797953730169</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.43515696946218</v>
+        <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.705401012214665</v>
+        <v>1.639898700586339</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.615232673022444</v>
+        <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6792857934852585</v>
+        <v>-0.7485298728371399</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.411203428486222</v>
+        <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.720441642945733</v>
+        <v>1.654939331317407</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.351172734699647</v>
+        <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5869221343178923</v>
+        <v>-0.6561662136697732</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.147143490163427</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.865617289777658</v>
+        <v>1.800114978149332</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.64409311119481</v>
+        <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3068773185762579</v>
+        <v>-0.3761213979281393</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.147143490163427</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.862830256117358</v>
+        <v>1.797327944489031</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.603908812828619</v>
+        <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2904599753419403</v>
+        <v>-0.3597040546938217</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.106959191797236</v>
+        <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.887284459024913</v>
+        <v>1.821782147396587</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626476</v>
+        <v>3.856161751626478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.440508941889256</v>
+        <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2257332057454384</v>
+        <v>-0.2949772850973194</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.943559320857873</v>
+        <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.984691202809288</v>
+        <v>1.919188891180962</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.207027719659656</v>
+        <v>-8.38013791803936</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.124416288015746</v>
+        <v>-0.1936603673676274</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.710078098628275</v>
+        <v>-1.819248618008818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.1327043649849</v>
+        <v>2.067202053356573</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.057361328652142</v>
+        <v>-8.230471527031845</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.06744194192569974</v>
+        <v>-0.1366860212775807</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.617174607385739</v>
+        <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.185554249417462</v>
+        <v>2.120051937789135</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.925085855021256</v>
+        <v>-8.098196053400958</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.0191642657263178</v>
+        <v>-0.08840834507819872</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.484899133754852</v>
+        <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.260287020343021</v>
+        <v>2.194784708714694</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.769347522461514</v>
+        <v>-7.942457720841216</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.04594612798521558</v>
+        <v>-0.02329795136666535</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.329160801195111</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.356545080566502</v>
+        <v>2.291042768938176</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.520347723777933</v>
+        <v>-7.693457922157635</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1584523886823068</v>
+        <v>0.08920830933042589</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.329160801195111</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.369451421790161</v>
+        <v>2.303949110161835</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.625937713551037</v>
+        <v>-7.79904791193074</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.01175953682615383</v>
+        <v>-0.08100361617803475</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.434750790968215</v>
+        <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.17812149832708</v>
+        <v>2.112619186698754</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.644672615669634</v>
+        <v>-7.817782814049337</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.02929084420349382</v>
+        <v>-0.03995323514838711</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.440346800628346</v>
+        <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.223308234408087</v>
+        <v>2.157805922779761</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.496732574262035</v>
+        <v>-7.669842772641737</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.03141206192163404</v>
+        <v>-0.100656141273515</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.420025884719789</v>
+        <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.115621861265054</v>
+        <v>2.050119549636728</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.443763052008046</v>
+        <v>-7.616873250387749</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.0189382392735169</v>
+        <v>-0.08818231862539783</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.3670563624658</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.138689588363969</v>
+        <v>2.073187276735643</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.400214645237356</v>
+        <v>-7.573324843617058</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.008479488660333878</v>
+        <v>-0.07772356801221481</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.3670563624658</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.131728976268876</v>
+        <v>2.06622666464055</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.158066251783498</v>
+        <v>-7.3311764501632</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1028422231023525</v>
+        <v>0.03359814375047154</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.3670563624658</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.146191330650019</v>
+        <v>2.080689019021693</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.049807114660976</v>
+        <v>-7.222917313040679</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1406779984105562</v>
+        <v>0.07143391905867524</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.3670563624658</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.140723451109214</v>
+        <v>2.075221139480888</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.926515979843845</v>
+        <v>-7.099626178223548</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1874925463479853</v>
+        <v>0.1182484669961044</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.243765227648669</v>
+        <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.212196226010069</v>
+        <v>2.146693914381743</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.905366780940402</v>
+        <v>-7.078476979320104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2036532041466881</v>
+        <v>0.1344091247948072</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.222616028745226</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.232586723589461</v>
+        <v>2.167084411961135</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.661601338956958</v>
+        <v>-6.83471153733666</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2969400892871161</v>
+        <v>0.2276960099352352</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.222616028745226</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.228367431936511</v>
+        <v>2.162865120308185</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.559838518679663</v>
+        <v>-6.732948717059365</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3397695313180504</v>
+        <v>0.2705254519661695</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.209396960352797</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.238423186891985</v>
+        <v>2.172920875263658</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.309988124730588</v>
+        <v>-6.483098323110291</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4324517638813821</v>
+        <v>0.3632076845295011</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.209396960352797</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.231165261875687</v>
+        <v>2.165662950247361</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.134096032263155</v>
+        <v>-6.307206230642858</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5064077243890042</v>
+        <v>0.4371636450371228</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.209396960352797</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.234764385396335</v>
+        <v>2.169262073768009</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.962649569240692</v>
+        <v>-6.135759767620395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5883138156525431</v>
+        <v>0.5190697363006618</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.037950497330334</v>
+        <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.350959769264367</v>
+        <v>2.285457457636041</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.888360003502353</v>
+        <v>-6.061470201882056</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6170501195641758</v>
+        <v>0.5478060402122944</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9636609315919948</v>
+        <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.394553986323668</v>
+        <v>2.329051674695342</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.824724261268418</v>
+        <v>-5.997834459648121</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6471992175120671</v>
+        <v>0.5779551381601857</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9000251893580603</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.437430232718346</v>
+        <v>2.37192792109002</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074786</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.713297501942498</v>
+        <v>-5.886407700322201</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6729641800262307</v>
+        <v>0.6037201006743493</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9000251893580603</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.418624491502142</v>
+        <v>2.353122179873815</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242298</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.472867005137638</v>
+        <v>-5.645977203517341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.770879455373052</v>
+        <v>0.7016353760211711</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6595946925532</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.564625866209935</v>
+        <v>2.499123554581609</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.400624436966443</v>
+        <v>-5.573734635346146</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8037057964763501</v>
+        <v>0.7344617171244692</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6595946925532</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.568555180044755</v>
+        <v>2.503052868416429</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.347626114685055</v>
+        <v>-5.520736313064758</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8255837093062453</v>
+        <v>0.7563396299543643</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6042584335512612</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.602435519363258</v>
+        <v>2.536933207734932</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.238821229205328</v>
+        <v>-5.411931427585031</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8661037347181297</v>
+        <v>0.7968596553662484</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6042584335512612</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.599433590583252</v>
+        <v>2.533931278954926</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675941</v>
+        <v>3.818668951675944</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.018800431168318</v>
+        <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9556910909435481</v>
+        <v>0.8864470115916667</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4630385884832809</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.685744534634654</v>
+        <v>2.620242223006328</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539955</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.88593274210504</v>
+        <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.024732349370682</v>
+        <v>0.955488270018801</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4630385884832809</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.701638717436477</v>
+        <v>2.636136405808151</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.765759658740541</v>
+        <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.073947427156784</v>
+        <v>1.004703347804903</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.342865505118782</v>
+        <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.774888411895479</v>
+        <v>2.709386100267153</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.621087513640804</v>
+        <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.141904387758119</v>
+        <v>1.072660308406237</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1981933600190446</v>
+        <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.871779801516761</v>
+        <v>2.806277489888435</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.680962340998496</v>
+        <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.103991948216468</v>
+        <v>1.034747868864586</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2580681873767367</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.821892396503571</v>
+        <v>2.756390084875245</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.594162843219488</v>
+        <v>-4.767273041599191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.161112240650637</v>
+        <v>1.091868161298756</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2580681873767367</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.844292889826137</v>
+        <v>2.778790578197811</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.596632549681294</v>
+        <v>-4.769742748060997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.160196759439327</v>
+        <v>1.090952680087445</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2605378938385429</v>
+        <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.842883467322466</v>
+        <v>2.77738115569414</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.665002736005304</v>
+        <v>-4.838112934385007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.143855607384425</v>
+        <v>1.074611528032543</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2512621948023279</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.859455809218897</v>
+        <v>2.793953497590571</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.678790788852351</v>
+        <v>-4.851900987232054</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.128777094877497</v>
+        <v>1.059533015525616</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2512621948023279</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.849892517850789</v>
+        <v>2.784390206222462</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.709783948181056</v>
+        <v>-4.882894146560759</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.941089396186402</v>
+        <v>0.8718453168345206</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2512621948023279</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.674602082891175</v>
+        <v>2.609099771262849</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.534309688388587</v>
+        <v>-4.707419886768291</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.015846332095177</v>
+        <v>0.946602252743296</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2512621948023279</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.679169314882963</v>
+        <v>2.613667003254637</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225446</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.645245941029836</v>
+        <v>-4.81835613940954</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9472138597998847</v>
+        <v>0.8779697804480033</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2512621948023279</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.65491134364417</v>
+        <v>2.589409032015844</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.611582395557554</v>
+        <v>-4.784692593937257</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9638106632087031</v>
+        <v>0.8945665838568218</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2175986493300461</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.678240856147445</v>
+        <v>2.612738544519118</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.551729776353831</v>
+        <v>-4.724839974733534</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9979240973223247</v>
+        <v>0.9286800179704435</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2175986493300461</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.688413242579577</v>
+        <v>2.622910930951251</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.465486313327453</v>
+        <v>-4.638596511707156</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.027367753106736</v>
+        <v>0.9581236737548549</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2175986493300461</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.683359513153437</v>
+        <v>2.617857201525111</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.75202749931605</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.510793132726433</v>
+        <v>-4.683903331106136</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.00102080079167</v>
+        <v>0.9317767214397885</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2584088123392769</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.650649190792425</v>
+        <v>2.585146879164098</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.539826237428734</v>
+        <v>-4.712936435808437</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9899594319438509</v>
+        <v>0.9207153525919696</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2584088123392769</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.651201063825526</v>
+        <v>2.5856987521972</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.447015755977874</v>
+        <v>-4.620125954357578</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9563563164155604</v>
+        <v>0.887112237063679</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1655983308884175</v>
+        <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.636160044587407</v>
+        <v>2.570657732959081</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.491405225307302</v>
+        <v>-4.664515423687005</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9404740046083901</v>
+        <v>0.871229925256509</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2099878002178452</v>
+        <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.611399838914351</v>
+        <v>2.545897527286025</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.378734007071052</v>
+        <v>-4.551844205450755</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9806182004146133</v>
+        <v>0.911374121062732</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.09731658198159499</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.674078278367825</v>
+        <v>2.608575966739498</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.266357005888379</v>
+        <v>-4.439467204268082</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.03106029671835</v>
+        <v>0.9618162173664684</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.09731658198159499</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.679569574198492</v>
+        <v>2.614067262570166</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498868</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.294137403789732</v>
+        <v>-4.467247602169435</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.031445339326348</v>
+        <v>0.9622012599744665</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.125096979882948</v>
+        <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.674398537226219</v>
+        <v>2.608896225597893</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705329</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.37713868481501</v>
+        <v>-4.550248883194714</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8366005469168893</v>
+        <v>0.7673564675650082</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1436678644101218</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.501611726510568</v>
+        <v>2.436109414882242</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729273</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.485752763258342</v>
+        <v>-4.658862961638045</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9133045762587626</v>
+        <v>0.8440604969068812</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1436678644101218</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.621761387229774</v>
+        <v>2.556259075601448</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190772</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.450343725010199</v>
+        <v>-4.623453923389902</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9419812176603428</v>
+        <v>0.8727371383084614</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1436678644101218</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.636274413332097</v>
+        <v>2.570772101703771</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.74117406991343</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.411960062452048</v>
+        <v>-4.585070260831751</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9547541240259718</v>
+        <v>0.8855100446740907</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1052842018519706</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.656724052209356</v>
+        <v>2.59122174058103</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.75114719753249</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.234843732416882</v>
+        <v>-4.407953930796585</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.02232968488534</v>
+        <v>0.9530856055334589</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1052842018519706</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.653453081054658</v>
+        <v>2.587950769426332</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793906</v>
+        <v>3.741328448793908</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.279935977250427</v>
+        <v>-4.45304617563013</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.004976178713835</v>
+        <v>0.9357320993619538</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1671802450213604</v>
+        <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.616998846914937</v>
+        <v>2.551496535286611</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011239</v>
+        <v>3.750729377011241</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.10056055601166</v>
+        <v>-4.273670754391363</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.070513322515756</v>
+        <v>1.001269243163875</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.01040348685064174</v>
+        <v>-0.1195740062311853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.704851877123783</v>
+        <v>2.639349565495456</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982233</v>
+        <v>3.716991718982235</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.145574769532265</v>
+        <v>-4.318684967911969</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.033315092439104</v>
+        <v>0.9640710130872225</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.04075238216524635</v>
+        <v>-0.1499229015457899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.66744999526661</v>
+        <v>2.601947683638284</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509544</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.4125792798047</v>
+        <v>-4.585689478184404</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9322048506690757</v>
+        <v>0.8629607713171943</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2351154202081949</v>
+        <v>-0.3442859395887385</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.556523734779786</v>
+        <v>2.49102142315146</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.513777061241873</v>
+        <v>-4.686887259621576</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8909296599907079</v>
+        <v>0.8216855806388268</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3035242337535141</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.514682368549096</v>
+        <v>2.44918005692077</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.481301475071101</v>
+        <v>-4.654411673450804</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9015198560133335</v>
+        <v>0.8322757766614524</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3035242337535141</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.512282330103413</v>
+        <v>2.446780018475087</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.462263347363804</v>
+        <v>-4.635373545743507</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9056598263044975</v>
+        <v>0.8364157469526161</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3617078450847087</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.473896882512941</v>
+        <v>2.408394570884615</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131255</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.493389978514422</v>
+        <v>-4.666500176894125</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.070791042782931</v>
+        <v>1.001546963431049</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3617078450847087</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.651478751451622</v>
+        <v>2.585976439823296</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067869</v>
+        <v>3.722447362067871</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.50725673984834</v>
+        <v>-4.680366938228043</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.066077667235497</v>
+        <v>0.9968335878836156</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3995657618185316</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.629597330397461</v>
+        <v>2.564095018769136</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789127</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.46245256830841</v>
+        <v>-4.635562766688113</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.090007866248395</v>
+        <v>1.020763786896514</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3995657618185316</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.635605860794387</v>
+        <v>2.570103549166062</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.781501250519914</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.314709598073407</v>
+        <v>-4.487819796453111</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.228257702134418</v>
+        <v>1.159013622782537</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2317584045836484</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.815442922927339</v>
+        <v>2.749940611299013</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181174</v>
+        <v>3.802245929181176</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.416724280604629</v>
+        <v>-4.589834478984332</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.19024545065341</v>
+        <v>1.121001371301529</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2317584045836484</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.81823654445882</v>
+        <v>2.752734232830494</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394737</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.410571574551844</v>
+        <v>-4.583681772931548</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.193368881466182</v>
+        <v>1.124124802114301</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2256056985308642</v>
+        <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.822590516482149</v>
+        <v>2.757088204853823</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.427380872702346</v>
+        <v>-4.600491071082049</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.185725638946092</v>
+        <v>1.116481559594211</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2424149966813658</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.811585414331959</v>
+        <v>2.746083102703632</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.86736263679843</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.365082873926224</v>
+        <v>-4.538193072305927</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.276980392253362</v>
+        <v>1.20773631290148</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2424149966813658</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.877920968128779</v>
+        <v>2.812418656500453</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992195</v>
+        <v>3.848729139992197</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.163292676261066</v>
+        <v>-4.336402874640769</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.066277343708823</v>
+        <v>0.9970332643569417</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.0443968045122114</v>
+        <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.70531275581967</v>
+        <v>2.639810444191344</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.08991457917233</v>
+        <v>-4.263024777552033</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.165918814866493</v>
+        <v>1.096674735514611</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.02898129257652515</v>
+        <v>-0.08018922680401847</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.819629846395087</v>
+        <v>2.754127534766761</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319549</v>
+        <v>3.819063300319551</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.187655123797304</v>
+        <v>-4.360765322177008</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.141450333132547</v>
+        <v>1.072206253780665</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.01309201444354496</v>
+        <v>-0.09607850493699865</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.824724015631343</v>
+        <v>2.759221704003016</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.83181903248939</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.363992883920234</v>
+        <v>-4.537103082299937</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.069451209908046</v>
+        <v>1.000207130556165</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1632457456793844</v>
+        <v>-0.2724162650599281</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.717457340382257</v>
+        <v>2.65195502875393</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397797</v>
+        <v>3.8364116723978</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.287570837488307</v>
+        <v>-4.46068103586801</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.098511646520746</v>
+        <v>1.029267567168864</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1632457456793844</v>
+        <v>-0.2724162650599281</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.715948958422185</v>
+        <v>2.650446646793859</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024965</v>
+        <v>3.836023391024968</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.243197705849738</v>
+        <v>-4.416307904229441</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.116123766611609</v>
+        <v>1.046879687259728</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1188726140408158</v>
+        <v>-0.2280431334213595</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.742435704840763</v>
+        <v>2.676933393212436</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.235243735554966</v>
+        <v>-4.408353933934669</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.119305354729518</v>
+        <v>1.050061275377637</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1188726140408158</v>
+        <v>-0.2280431334213595</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.742435704840763</v>
+        <v>2.676933393212436</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.18758800499391</v>
+        <v>-4.360698203373613</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.144749403981745</v>
+        <v>1.075505324629864</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.07121688347976018</v>
+        <v>-0.1803874028603038</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.777410900205201</v>
+        <v>2.711908588576875</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.822707244326878</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.059903695199614</v>
+        <v>-4.233013893579317</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.200715501274189</v>
+        <v>1.131471421922307</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.05646742631453627</v>
+        <v>-0.05270309306600734</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.858913859456504</v>
+        <v>2.793411547828177</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.828837911314554</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.120570285602003</v>
+        <v>-4.293680483981706</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.163203537589105</v>
+        <v>1.093959458237224</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.0252308904039974</v>
+        <v>-0.134401409784541</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.796649541901255</v>
+        <v>2.731147230272929</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.075731883993605</v>
+        <v>-4.248842082373308</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.185236600843093</v>
+        <v>1.115992521491212</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.02068745745912792</v>
+        <v>-0.1298579768396715</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.803473304278806</v>
+        <v>2.737970992650479</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.176490519750603</v>
+        <v>-4.349600718130306</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.149094086171372</v>
+        <v>1.079850006819491</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1095130261861333</v>
+        <v>-0.218683545566677</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.75433890267368</v>
+        <v>2.688836591045354</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163221</v>
+        <v>3.826713779163223</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.132287682664702</v>
+        <v>-4.305397881044406</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.172654823533569</v>
+        <v>1.103410744181688</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.0653101891002329</v>
+        <v>-0.1744807084807765</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.786740207453058</v>
+        <v>2.721237895824732</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.169266710328145</v>
+        <v>-4.342376908707848</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.15627321293744</v>
+        <v>1.087029133585558</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.02833628730890236</v>
+        <v>-0.137506806689446</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.807334548997104</v>
+        <v>2.741832237368778</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.189324789192986</v>
+        <v>-4.362434987572689</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.199497746574543</v>
+        <v>1.130253667222662</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.02833628730890236</v>
+        <v>-0.137506806689446</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.858582314180143</v>
+        <v>2.793080002551817</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.149394116015095</v>
+        <v>-4.322504314394799</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.213910720439952</v>
+        <v>1.144666641088071</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.01159438586898798</v>
+        <v>-0.09757613351155564</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.880981422681131</v>
+        <v>2.815479111052805</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232401</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.098362023292568</v>
+        <v>-4.271472221672271</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.229271785767233</v>
+        <v>1.160027706415352</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.06262647859151593</v>
+        <v>-0.04654404078902769</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.906548906552918</v>
+        <v>2.841046594924591</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.033137842165362</v>
+        <v>-4.206248040545066</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.27254886231082</v>
+        <v>1.203304782958939</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1278506597187216</v>
+        <v>0.01868014033817794</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.962870819321946</v>
+        <v>2.89736850769362</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.84009022063982</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.995710822094229</v>
+        <v>-4.168821020473931</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.283480642638554</v>
+        <v>1.214236563286673</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1331021977479032</v>
+        <v>0.0239316783673596</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.961982714438735</v>
+        <v>2.896480402810409</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749923</v>
+        <v>3.845198842749925</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.015822478128936</v>
+        <v>-4.105787511438455</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.276692772555911</v>
+        <v>1.240706759232104</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1441295427453224</v>
+        <v>0.0690559626676161</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.969855913768427</v>
+        <v>2.924811765721803</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393549</v>
+        <v>3.828690479393551</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.962077663701732</v>
+        <v>-4.05204269701125</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.458748469348004</v>
+        <v>1.422762456024197</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1541928521857844</v>
+        <v>0.07911927210807806</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.136451670453915</v>
+        <v>3.091407522407291</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714887</v>
+        <v>3.813251854714889</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.938286095095589</v>
+        <v>-4.028251128405108</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.588378006008278</v>
+        <v>1.552391992684471</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1779844207919267</v>
+        <v>0.1029108407142204</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.270839520835418</v>
+        <v>3.225795372788794</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756013</v>
+        <v>3.814259761756015</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.912202010831781</v>
+        <v>-4.0021670441413</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.59051961572766</v>
+        <v>1.554533602403853</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1779844207919267</v>
+        <v>0.1029108407142204</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.262547496849276</v>
+        <v>3.217503348802653</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654187</v>
+        <v>3.803426852654189</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.907867707774733</v>
+        <v>-3.997832741084252</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.590446532534259</v>
+        <v>1.554460519210452</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3296345241111306</v>
+        <v>0.2545609440334243</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.351730754424578</v>
+        <v>3.306686606377955</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717118</v>
+        <v>3.79629317771712</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.89897524638145</v>
+        <v>-3.988940279690969</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.611557922818364</v>
+        <v>1.575571909494556</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3296345241111306</v>
+        <v>0.2545609440334243</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.36928516015137</v>
+        <v>3.324241012104746</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702627</v>
+        <v>3.794453975702629</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.067451363351327</v>
+        <v>-4.157416396660846</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.536022523434997</v>
+        <v>1.500036510111189</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3016866883945498</v>
+        <v>0.2266131083168435</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.344371506126005</v>
+        <v>3.299327358079381</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539971</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.369651834489744</v>
+        <v>-3.459616867799263</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.796412032167492</v>
+        <v>1.760426018843684</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2313386290241391</v>
+        <v>0.1562650489464328</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.283432367691621</v>
+        <v>3.238388219644997</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389899</v>
+        <v>3.784700379389901</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.346930730806591</v>
+        <v>-3.43689576411611</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.796164496137658</v>
+        <v>1.76017848281385</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2313386290241391</v>
+        <v>0.1562650489464328</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.274096390188525</v>
+        <v>3.229052242141901</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534937</v>
+        <v>3.783234730534939</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.345205687516548</v>
+        <v>-3.435170720826067</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.955760639304844</v>
+        <v>1.919774625981036</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2330636723141828</v>
+        <v>0.1579900922364765</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.434037542013721</v>
+        <v>3.388993393967096</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401675</v>
+        <v>3.779962759401677</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.499986694294803</v>
+        <v>-3.589951727604322</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.930926059087189</v>
+        <v>1.894940045763381</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1996959982597067</v>
+        <v>0.1246224181820004</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.451094760074681</v>
+        <v>3.406050612028058</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557224</v>
+        <v>3.769472653557225</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.56724713831672</v>
+        <v>-3.657212171626239</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.900697237467967</v>
+        <v>1.864711224144159</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1324355542377896</v>
+        <v>0.05736197416008332</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.407413849651076</v>
+        <v>3.362369701604452</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088379</v>
+        <v>3.76670253008838</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.544775604277888</v>
+        <v>-3.634740637587407</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.919692004728241</v>
+        <v>1.883705991404434</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2681410390537609</v>
+        <v>0.1930674589760545</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.4988432941854</v>
+        <v>3.453799146138777</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541371</v>
+        <v>3.768081101541373</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.680728612334204</v>
+        <v>-3.770693645643723</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.049413933650674</v>
+        <v>2.013427920326867</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2681410390537609</v>
+        <v>0.1930674589760545</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.68294642633036</v>
+        <v>3.637902278283736</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.844835778241961</v>
+        <v>3.823246158000823</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.868019902881184</v>
+        <v>-3.881637610990702</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.966614112334875</v>
+        <v>1.961167029091068</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2681410390537609</v>
+        <v>0.1930674589760545</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.675063121233353</v>
+        <v>3.63001897318673</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240624.xlsx
+++ b/tame_output/ON/bt/strategyON_20240624.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.1%</t>
+          <t>-69.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-549.7%</t>
+          <t>-540.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>121.8%</t>
+          <t>121.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-180.1%</t>
+          <t>-176.6%</t>
         </is>
       </c>
     </row>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982235</v>
+        <v>3.716991718982236</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509544</v>
+        <v>3.737026608509545</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378105</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -47643,10 +47643,10 @@
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.881637610990702</v>
+        <v>-3.793101763448595</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.961167029091068</v>
+        <v>1.996581368107911</v>
       </c>
       <c r="F2004" t="n">
         <v>0.1930674589760545</v>

--- a/tame_output/ON/bt/strategyON_20240624.xlsx
+++ b/tame_output/ON/bt/strategyON_20240624.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>26.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.6%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>460.8%</t>
+          <t>456.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-540.9%</t>
+          <t>-554.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>121.9%</t>
+          <t>120.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.6%</t>
+          <t>-182.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-172.2%</t>
+          <t>-168.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-204.7%</t>
+          <t>-217.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-83.0%</t>
+          <t>-90.9%</t>
         </is>
       </c>
     </row>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839727</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388732</v>
+        <v>3.839374447388731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626478</v>
+        <v>3.856161751626477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987905</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318095</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057528</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011501</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883076</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074786</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242298</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367688</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879969</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502342</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675944</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.191910629548021</v>
+        <v>-5.245769611197967</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8864470115916667</v>
+        <v>0.8649034189316884</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.669006831468856</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620242223006328</v>
+        <v>2.562163588843309</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539955</v>
+        <v>3.843274527539953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.059042940484743</v>
+        <v>-5.112901922134689</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.955488270018801</v>
+        <v>0.9339446773588227</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.669006831468856</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636136405808151</v>
+        <v>2.578057771645133</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.938869857120245</v>
+        <v>-4.992728838770191</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.004703347804903</v>
+        <v>0.983159755144924</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4520360244993256</v>
+        <v>-0.548833748104357</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.709386100267153</v>
+        <v>2.651307466104134</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.794197712020507</v>
+        <v>-4.848056693670453</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.072660308406237</v>
+        <v>1.051116715746259</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3073638793995881</v>
+        <v>-0.4041616030046196</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.806277489888435</v>
+        <v>2.748198855725416</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.854072539378199</v>
+        <v>-4.907931521028146</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.034747868864586</v>
+        <v>1.013204276204608</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.4640364303623117</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.756390084875245</v>
+        <v>2.698311450712227</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.767273041599191</v>
+        <v>-4.821132023249136</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.091868161298756</v>
+        <v>1.070324568638778</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.4640364303623117</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.778790578197811</v>
+        <v>2.720711944034793</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.769742748060997</v>
+        <v>-4.823601729710942</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.090952680087445</v>
+        <v>1.069409087427467</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3697084132190864</v>
+        <v>-0.4665061368241179</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.77738115569414</v>
+        <v>2.719302521531121</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.838112934385007</v>
+        <v>-4.891971916034953</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074611528032543</v>
+        <v>1.053067935372565</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.457230437787903</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.793953497590571</v>
+        <v>2.735874863427552</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.851900987232054</v>
+        <v>-4.905759968881999</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.059533015525616</v>
+        <v>1.037989422865638</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.457230437787903</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.784390206222462</v>
+        <v>2.726311572059443</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.882894146560759</v>
+        <v>-4.936753128210705</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8718453168345206</v>
+        <v>0.8503017241745425</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.457230437787903</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.609099771262849</v>
+        <v>2.55102113709983</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.707419886768291</v>
+        <v>-4.761278868418236</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.946602252743296</v>
+        <v>0.9250586600833177</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.457230437787903</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.613667003254637</v>
+        <v>2.555588369091618</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.81835613940954</v>
+        <v>-4.872215121059485</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8779697804480033</v>
+        <v>0.8564261877880253</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.457230437787903</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.589409032015844</v>
+        <v>2.531330397852825</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.784692593937257</v>
+        <v>-4.838551575587203</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8945665838568218</v>
+        <v>0.8730229911968437</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.4235668923156211</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.612738544519118</v>
+        <v>2.554659910356099</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.724839974733534</v>
+        <v>-4.778698956383479</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9286800179704435</v>
+        <v>0.9071364253104655</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.4235668923156211</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.622910930951251</v>
+        <v>2.564832296788232</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.638596511707156</v>
+        <v>-4.692455493357102</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9581236737548549</v>
+        <v>0.9365800810948768</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.4235668923156211</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.617857201525111</v>
+        <v>2.559778567362092</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202749931605</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.683903331106136</v>
+        <v>-4.737762312756082</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9317767214397885</v>
+        <v>0.9102331287798104</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.4643770553248519</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.585146879164098</v>
+        <v>2.527068245001079</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.712936435808437</v>
+        <v>-4.766795417458383</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9207153525919696</v>
+        <v>0.8991717599319915</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.4643770553248519</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.5856987521972</v>
+        <v>2.527620118034181</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.620125954357578</v>
+        <v>-4.673984936007523</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.887112237063679</v>
+        <v>0.865568644403701</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2747688502689611</v>
+        <v>-0.3715665738739926</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.570657732959081</v>
+        <v>2.512579098796062</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.664515423687005</v>
+        <v>-4.718374405336951</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.871229925256509</v>
+        <v>0.8496863325965309</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3191583195983888</v>
+        <v>-0.4159560432034202</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.545897527286025</v>
+        <v>2.487818893123007</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.551844205450755</v>
+        <v>-4.6057031871007</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.911374121062732</v>
+        <v>0.8898305284027539</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.30328482496717</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.608575966739498</v>
+        <v>2.55049733257648</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798541</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.439467204268082</v>
+        <v>-4.493326185918027</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9618162173664684</v>
+        <v>0.9402726247064903</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.30328482496717</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.614067262570166</v>
+        <v>2.555988628407147</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498868</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.467247602169435</v>
+        <v>-4.52110658381938</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9622012599744665</v>
+        <v>0.9406576673144884</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2342674992634916</v>
+        <v>-0.3310652228685231</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608896225597893</v>
+        <v>2.550817591434874</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705329</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.550248883194714</v>
+        <v>-4.604107864844659</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7673564675650082</v>
+        <v>0.7458128749050301</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.3496361073956968</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.436109414882242</v>
+        <v>2.378030780719223</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729273</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.658862961638045</v>
+        <v>-4.71272194328799</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8440604969068812</v>
+        <v>0.8225169042469032</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.3496361073956968</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556259075601448</v>
+        <v>2.498180441438429</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190772</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.623453923389902</v>
+        <v>-4.677312905039847</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8727371383084614</v>
+        <v>0.8511935456484834</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.3496361073956968</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570772101703771</v>
+        <v>2.512693467540752</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.74117406991343</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.585070260831751</v>
+        <v>-4.638929242481696</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8855100446740907</v>
+        <v>0.8639664520141124</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.3112524448375457</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.59122174058103</v>
+        <v>2.533143106418011</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114719753249</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.407953930796585</v>
+        <v>-4.46181291244653</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9530856055334589</v>
+        <v>0.9315420128734808</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.3112524448375457</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587950769426332</v>
+        <v>2.529872135263313</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793908</v>
+        <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.45304617563013</v>
+        <v>-4.506905157280076</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9357320993619538</v>
+        <v>0.9141885067019757</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.276350764401904</v>
+        <v>-0.3731484880069355</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.551496535286611</v>
+        <v>2.493417901123592</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011241</v>
+        <v>3.750729377011239</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.273670754391363</v>
+        <v>-4.327529736041308</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.001269243163875</v>
+        <v>0.9797256505038971</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1195740062311853</v>
+        <v>-0.2163717298362168</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.639349565495456</v>
+        <v>2.581270931332438</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982236</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.318684967911969</v>
+        <v>-4.372543949561914</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9640710130872225</v>
+        <v>0.9425274204272445</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1499229015457899</v>
+        <v>-0.2467206251508214</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.601947683638284</v>
+        <v>2.543869049475265</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509545</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.585689478184404</v>
+        <v>-4.639548459834349</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8629607713171943</v>
+        <v>0.8414171786572162</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3442859395887385</v>
+        <v>-0.44108366319377</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.49102142315146</v>
+        <v>2.432942788988441</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.686887259621576</v>
+        <v>-4.740746241271522</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8216855806388268</v>
+        <v>0.8001419879788485</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.5094924767390892</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.44918005692077</v>
+        <v>2.391101422757751</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70557166181546</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.654411673450804</v>
+        <v>-4.708270655100749</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8322757766614524</v>
+        <v>0.8107321840014743</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.5094924767390892</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.446780018475087</v>
+        <v>2.388701384312068</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378105</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.635373545743507</v>
+        <v>-4.689232527393452</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8364157469526161</v>
+        <v>0.814872154292638</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.5676760880702837</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.408394570884615</v>
+        <v>2.350315936721596</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131255</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.666500176894125</v>
+        <v>-4.720359158544071</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.001546963431049</v>
+        <v>0.9800033707710711</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.5676760880702837</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.585976439823296</v>
+        <v>2.527897805660277</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067871</v>
+        <v>3.722447362067869</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.680366938228043</v>
+        <v>-4.734225919877988</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9968335878836156</v>
+        <v>0.9752899952236376</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.6055340048041066</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564095018769136</v>
+        <v>2.506016384606117</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789127</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.635562766688113</v>
+        <v>-4.689421748338058</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.020763786896514</v>
+        <v>0.9992201942365355</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.6055340048041066</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570103549166062</v>
+        <v>2.512024915003042</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519914</v>
+        <v>3.781501250519912</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.487819796453111</v>
+        <v>-4.541678778103056</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.159013622782537</v>
+        <v>1.137470030122558</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.4377266475692234</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.749940611299013</v>
+        <v>2.691861977135994</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181176</v>
+        <v>3.802245929181174</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.589834478984332</v>
+        <v>-4.643693460634277</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.121001371301529</v>
+        <v>1.099457778641551</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.4377266475692234</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752734232830494</v>
+        <v>2.694655598667475</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394737</v>
+        <v>3.805608985394735</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.583681772931548</v>
+        <v>-4.637540754581493</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.124124802114301</v>
+        <v>1.102581209454323</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3347762179114078</v>
+        <v>-0.4315739415164391</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.757088204853823</v>
+        <v>2.699009570690804</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.600491071082049</v>
+        <v>-4.654350052731995</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.116481559594211</v>
+        <v>1.094937966934233</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.4483832396669408</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746083102703632</v>
+        <v>2.688004468540613</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86736263679843</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.538193072305927</v>
+        <v>-4.592052053955872</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.20773631290148</v>
+        <v>1.186192720241502</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.4483832396669408</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.812418656500453</v>
+        <v>2.754340022337434</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992197</v>
+        <v>3.848729139992195</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.336402874640769</v>
+        <v>-4.390261856290715</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9970332643569417</v>
+        <v>0.9754896716969634</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.153567323892755</v>
+        <v>-0.2503650474977864</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.639810444191344</v>
+        <v>2.581731810028325</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.263024777552033</v>
+        <v>-4.316883759201978</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.096674735514611</v>
+        <v>1.075131142854633</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.08018922680401847</v>
+        <v>-0.1769869504090498</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.754127534766761</v>
+        <v>2.696048900603742</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319551</v>
+        <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.360765322177008</v>
+        <v>-4.414624303826953</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.072206253780665</v>
+        <v>1.050662661120687</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.09607850493699865</v>
+        <v>-0.19287622854203</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.759221704003016</v>
+        <v>2.701143069839998</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248939</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.537103082299937</v>
+        <v>-4.590962063949882</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.000207130556165</v>
+        <v>0.978663537896187</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2724162650599281</v>
+        <v>-0.3692139886649594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.65195502875393</v>
+        <v>2.593876394590912</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.8364116723978</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.46068103586801</v>
+        <v>-4.514540017517955</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.029267567168864</v>
+        <v>1.007723974508886</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2724162650599281</v>
+        <v>-0.3692139886649594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.650446646793859</v>
+        <v>2.59236801263084</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024968</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.416307904229441</v>
+        <v>-4.470166885879387</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.046879687259728</v>
+        <v>1.02533609459975</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2280431334213595</v>
+        <v>-0.3248408570263908</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.676933393212436</v>
+        <v>2.618854759049418</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.408353933934669</v>
+        <v>-4.462212915584614</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.050061275377637</v>
+        <v>1.028517682717659</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2280431334213595</v>
+        <v>-0.3248408570263908</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.676933393212436</v>
+        <v>2.618854759049418</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.360698203373613</v>
+        <v>-4.414557185023559</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.075505324629864</v>
+        <v>1.053961731969886</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1803874028603038</v>
+        <v>-0.2771851264653352</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.711908588576875</v>
+        <v>2.653829954413855</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326878</v>
+        <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.233013893579317</v>
+        <v>-4.286872875229262</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.131471421922307</v>
+        <v>1.109927829262329</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.05270309306600734</v>
+        <v>-0.1495008166710387</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.793411547828177</v>
+        <v>2.735332913665158</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314554</v>
+        <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.293680483981706</v>
+        <v>-4.347539465631652</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.093959458237224</v>
+        <v>1.072415865577246</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.134401409784541</v>
+        <v>-0.2311991333895724</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.731147230272929</v>
+        <v>2.673068596109911</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.248842082373308</v>
+        <v>-4.302701064023253</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.115992521491212</v>
+        <v>1.094448928831234</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1298579768396715</v>
+        <v>-0.2266557004447029</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.737970992650479</v>
+        <v>2.679892358487461</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.349600718130306</v>
+        <v>-4.403459699780251</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.079850006819491</v>
+        <v>1.058306414159512</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.218683545566677</v>
+        <v>-0.3154812691717083</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.688836591045354</v>
+        <v>2.630757956882335</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163223</v>
+        <v>3.826713779163221</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.305397881044406</v>
+        <v>-4.359256862694351</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.103410744181688</v>
+        <v>1.08186715152171</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1744807084807765</v>
+        <v>-0.2712784320858079</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.721237895824732</v>
+        <v>2.663159261661713</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.342376908707848</v>
+        <v>-4.396235890357794</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.087029133585558</v>
+        <v>1.06548554092558</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.137506806689446</v>
+        <v>-0.2343045302944773</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.741832237368778</v>
+        <v>2.683753603205759</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.362434987572689</v>
+        <v>-4.416293969222634</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.130253667222662</v>
+        <v>1.108710074562683</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.137506806689446</v>
+        <v>-0.2343045302944773</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.793080002551817</v>
+        <v>2.735001368388798</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078284</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.322504314394799</v>
+        <v>-4.376363296044744</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.144666641088071</v>
+        <v>1.123123048428093</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.09757613351155564</v>
+        <v>-0.194373857116587</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.815479111052805</v>
+        <v>2.757400476889786</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232401</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.271472221672271</v>
+        <v>-4.325331203322216</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.160027706415352</v>
+        <v>1.138484113755374</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.04654404078902769</v>
+        <v>-0.143341764394059</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.841046594924591</v>
+        <v>2.782967960761572</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162116</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.206248040545066</v>
+        <v>-4.260107022195011</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.203304782958939</v>
+        <v>1.181761190298961</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.01868014033817794</v>
+        <v>-0.07811758326685342</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.89736850769362</v>
+        <v>2.839289873530601</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84009022063982</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.168821020473931</v>
+        <v>-4.222680002123877</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.214236563286673</v>
+        <v>1.192692970626695</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.0239316783673596</v>
+        <v>-0.07286604523767176</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.896480402810409</v>
+        <v>2.83840176864739</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749925</v>
+        <v>3.845198842749923</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.105787511438455</v>
+        <v>-4.242791658158585</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.240706759232104</v>
+        <v>1.185905100544052</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0690559626676161</v>
+        <v>-0.06183870024025256</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.924811765721803</v>
+        <v>2.846274967977082</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393551</v>
+        <v>3.82869047939355</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.05204269701125</v>
+        <v>-4.18904684373138</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.422762456024197</v>
+        <v>1.367960797336145</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.07911927210807806</v>
+        <v>-0.0517753907997906</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.091407522407291</v>
+        <v>3.01287072466257</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714889</v>
+        <v>3.813251854714887</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.028251128405108</v>
+        <v>-4.165255275125238</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.552391992684471</v>
+        <v>1.497590333996419</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1029108407142204</v>
+        <v>-0.02798382219364831</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.225795372788794</v>
+        <v>3.147258575044072</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756015</v>
+        <v>3.814259761756013</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.0021670441413</v>
+        <v>-4.13917119086143</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.554533602403853</v>
+        <v>1.499731943715801</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1029108407142204</v>
+        <v>-0.02798382219364831</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.217503348802653</v>
+        <v>3.138966551057931</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654189</v>
+        <v>3.803426852654187</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.997832741084252</v>
+        <v>-4.134836887804382</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.554460519210452</v>
+        <v>1.4996588605224</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2545609440334243</v>
+        <v>0.1236662811255556</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.306686606377955</v>
+        <v>3.228149808633233</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79629317771712</v>
+        <v>3.796293177717118</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.988940279690969</v>
+        <v>-4.125944426411099</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.575571909494556</v>
+        <v>1.520770250806504</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2545609440334243</v>
+        <v>0.1236662811255556</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.324241012104746</v>
+        <v>3.245704214360025</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702629</v>
+        <v>3.794453975702627</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.157416396660846</v>
+        <v>-4.294420543380976</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.500036510111189</v>
+        <v>1.445234851423137</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2266131083168435</v>
+        <v>0.09571844540897484</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.299327358079381</v>
+        <v>3.22079056033466</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539971</v>
+        <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.459616867799263</v>
+        <v>-3.596621014519393</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.760426018843684</v>
+        <v>1.705624360155632</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1562650489464328</v>
+        <v>0.02537038603856412</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.238388219644997</v>
+        <v>3.159851421900275</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389901</v>
+        <v>3.784700379389899</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.43689576411611</v>
+        <v>-3.573899910836241</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.76017848281385</v>
+        <v>1.705376824125798</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1562650489464328</v>
+        <v>0.02537038603856412</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.229052242141901</v>
+        <v>3.15051544439718</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534939</v>
+        <v>3.783234730534937</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.435170720826067</v>
+        <v>-3.572174867546197</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.919774625981036</v>
+        <v>1.864972967292984</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1579900922364765</v>
+        <v>0.02709542932860787</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.388993393967096</v>
+        <v>3.310456596222375</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401677</v>
+        <v>3.779962759401675</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.589951727604322</v>
+        <v>-3.726955874324452</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.894940045763381</v>
+        <v>1.840138387075329</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1246224181820004</v>
+        <v>-0.006272244725868237</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.406050612028058</v>
+        <v>3.327513814283336</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557225</v>
+        <v>3.769472653557223</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.657212171626239</v>
+        <v>-3.794216318346369</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.864711224144159</v>
+        <v>1.809909565456107</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.05736197416008332</v>
+        <v>-0.07353268874778535</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.362369701604452</v>
+        <v>3.283832903859731</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76670253008838</v>
+        <v>3.766702530088378</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.634740637587407</v>
+        <v>-3.771744784307538</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.883705991404434</v>
+        <v>1.828904332716381</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1930674589760545</v>
+        <v>0.06217279606818588</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.453799146138777</v>
+        <v>3.375262348394056</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541373</v>
+        <v>3.768081101541371</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.770693645643723</v>
+        <v>-3.907697792363853</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.013427920326867</v>
+        <v>1.958626261638815</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1930674589760545</v>
+        <v>0.06217279606818588</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.637902278283736</v>
+        <v>3.559365480539015</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.823246158000823</v>
+        <v>3.542999933995473</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.793101763448595</v>
+        <v>-3.930105910168725</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.996581368107911</v>
+        <v>1.941779709419859</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1930674589760545</v>
+        <v>0.06217279606818588</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.63001897318673</v>
+        <v>3.551482175442009</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240624.xlsx
+++ b/tame_output/ON/bt/strategyON_20240624.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>54.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-69.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.4%</t>
+          <t>459.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-554.6%</t>
+          <t>-540.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-182.0%</t>
+          <t>-176.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-168.3%</t>
+          <t>-173.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-217.8%</t>
+          <t>-204.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-90.9%</t>
+          <t>-82.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2004"/>
+  <dimension ref="A1:G2005"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388731</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626477</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.245769611197967</v>
+        <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8649034189316884</v>
+        <v>0.8864470115916667</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.669006831468856</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.562163588843309</v>
+        <v>2.620242223006328</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539953</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.112901922134689</v>
+        <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9339446773588227</v>
+        <v>0.955488270018801</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.669006831468856</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.578057771645133</v>
+        <v>2.636136405808151</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.992728838770191</v>
+        <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.983159755144924</v>
+        <v>1.004703347804903</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.548833748104357</v>
+        <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.651307466104134</v>
+        <v>2.709386100267153</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.848056693670453</v>
+        <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.051116715746259</v>
+        <v>1.072660308406237</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4041616030046196</v>
+        <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.748198855725416</v>
+        <v>2.806277489888435</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.907931521028146</v>
+        <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.013204276204608</v>
+        <v>1.034747868864586</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4640364303623117</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.698311450712227</v>
+        <v>2.756390084875245</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.821132023249136</v>
+        <v>-4.767273041599191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.070324568638778</v>
+        <v>1.091868161298756</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4640364303623117</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.720711944034793</v>
+        <v>2.778790578197811</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.823601729710942</v>
+        <v>-4.769742748060997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.069409087427467</v>
+        <v>1.090952680087445</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4665061368241179</v>
+        <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.719302521531121</v>
+        <v>2.77738115569414</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.891971916034953</v>
+        <v>-4.838112934385007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.053067935372565</v>
+        <v>1.074611528032543</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.457230437787903</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.735874863427552</v>
+        <v>2.793953497590571</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.905759968881999</v>
+        <v>-4.851900987232054</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.037989422865638</v>
+        <v>1.059533015525616</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.457230437787903</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.726311572059443</v>
+        <v>2.784390206222462</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.936753128210705</v>
+        <v>-4.882894146560759</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8503017241745425</v>
+        <v>0.8718453168345206</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.457230437787903</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.55102113709983</v>
+        <v>2.609099771262849</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.761278868418236</v>
+        <v>-4.707419886768291</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9250586600833177</v>
+        <v>0.946602252743296</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.457230437787903</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.555588369091618</v>
+        <v>2.613667003254637</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225447</v>
+        <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.872215121059485</v>
+        <v>-4.81835613940954</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8564261877880253</v>
+        <v>0.8779697804480033</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.457230437787903</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.531330397852825</v>
+        <v>2.589409032015844</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.838551575587203</v>
+        <v>-4.784692593937257</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8730229911968437</v>
+        <v>0.8945665838568218</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4235668923156211</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.554659910356099</v>
+        <v>2.612738544519118</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.778698956383479</v>
+        <v>-4.724839974733534</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9071364253104655</v>
+        <v>0.9286800179704435</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4235668923156211</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.564832296788232</v>
+        <v>2.622910930951251</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.692455493357102</v>
+        <v>-4.638596511707156</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9365800810948768</v>
+        <v>0.9581236737548549</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4235668923156211</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.559778567362092</v>
+        <v>2.617857201525111</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.737762312756082</v>
+        <v>-4.683903331106136</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9102331287798104</v>
+        <v>0.9317767214397885</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4643770553248519</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.527068245001079</v>
+        <v>2.585146879164098</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.766795417458383</v>
+        <v>-4.712936435808437</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8991717599319915</v>
+        <v>0.9207153525919696</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4643770553248519</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.527620118034181</v>
+        <v>2.5856987521972</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.673984936007523</v>
+        <v>-4.620125954357578</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.865568644403701</v>
+        <v>0.887112237063679</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3715665738739926</v>
+        <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.512579098796062</v>
+        <v>2.570657732959081</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.718374405336951</v>
+        <v>-4.664515423687005</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8496863325965309</v>
+        <v>0.871229925256509</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4159560432034202</v>
+        <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.487818893123007</v>
+        <v>2.545897527286025</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.6057031871007</v>
+        <v>-4.551844205450755</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8898305284027539</v>
+        <v>0.911374121062732</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.30328482496717</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.55049733257648</v>
+        <v>2.608575966739498</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.493326185918027</v>
+        <v>-4.439467204268082</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9402726247064903</v>
+        <v>0.9618162173664684</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.30328482496717</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.555988628407147</v>
+        <v>2.614067262570166</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.52110658381938</v>
+        <v>-4.467247602169435</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9406576673144884</v>
+        <v>0.9622012599744665</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3310652228685231</v>
+        <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.550817591434874</v>
+        <v>2.608896225597893</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.604107864844659</v>
+        <v>-4.550248883194714</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7458128749050301</v>
+        <v>0.7673564675650082</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3496361073956968</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.378030780719223</v>
+        <v>2.436109414882242</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.71272194328799</v>
+        <v>-4.658862961638045</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8225169042469032</v>
+        <v>0.8440604969068812</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3496361073956968</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.498180441438429</v>
+        <v>2.556259075601448</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.677312905039847</v>
+        <v>-4.623453923389902</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8511935456484834</v>
+        <v>0.8727371383084614</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3496361073956968</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.512693467540752</v>
+        <v>2.570772101703771</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.638929242481696</v>
+        <v>-4.585070260831751</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8639664520141124</v>
+        <v>0.8855100446740907</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3112524448375457</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.533143106418011</v>
+        <v>2.59122174058103</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.46181291244653</v>
+        <v>-4.407953930796585</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9315420128734808</v>
+        <v>0.9530856055334589</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3112524448375457</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.529872135263313</v>
+        <v>2.587950769426332</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.506905157280076</v>
+        <v>-4.45304617563013</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9141885067019757</v>
+        <v>0.9357320993619538</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3731484880069355</v>
+        <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.493417901123592</v>
+        <v>2.551496535286611</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.327529736041308</v>
+        <v>-4.273670754391363</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9797256505038971</v>
+        <v>1.001269243163875</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2163717298362168</v>
+        <v>-0.1195740062311853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.581270931332438</v>
+        <v>2.639349565495456</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.372543949561914</v>
+        <v>-4.318684967911969</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9425274204272445</v>
+        <v>0.9640710130872225</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2467206251508214</v>
+        <v>-0.1499229015457899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.543869049475265</v>
+        <v>2.601947683638284</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.639548459834349</v>
+        <v>-4.585689478184404</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8414171786572162</v>
+        <v>0.8629607713171943</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.44108366319377</v>
+        <v>-0.3442859395887385</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.432942788988441</v>
+        <v>2.49102142315146</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.740746241271522</v>
+        <v>-4.686887259621576</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8001419879788485</v>
+        <v>0.8216855806388268</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5094924767390892</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.391101422757751</v>
+        <v>2.44918005692077</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.708270655100749</v>
+        <v>-4.654411673450804</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8107321840014743</v>
+        <v>0.8322757766614524</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5094924767390892</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.388701384312068</v>
+        <v>2.446780018475087</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.689232527393452</v>
+        <v>-4.635373545743507</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.814872154292638</v>
+        <v>0.8364157469526161</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5676760880702837</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.350315936721596</v>
+        <v>2.408394570884615</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.720359158544071</v>
+        <v>-4.666500176894125</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9800033707710711</v>
+        <v>1.001546963431049</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5676760880702837</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.527897805660277</v>
+        <v>2.585976439823296</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.734225919877988</v>
+        <v>-4.680366938228043</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9752899952236376</v>
+        <v>0.9968335878836156</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6055340048041066</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.506016384606117</v>
+        <v>2.564095018769136</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.689421748338058</v>
+        <v>-4.635562766688113</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9992201942365355</v>
+        <v>1.020763786896514</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6055340048041066</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.512024915003042</v>
+        <v>2.570103549166062</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.541678778103056</v>
+        <v>-4.487819796453111</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.137470030122558</v>
+        <v>1.159013622782537</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4377266475692234</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.691861977135994</v>
+        <v>2.749940611299013</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.643693460634277</v>
+        <v>-4.589834478984332</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.099457778641551</v>
+        <v>1.121001371301529</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4377266475692234</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.694655598667475</v>
+        <v>2.752734232830494</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394735</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.637540754581493</v>
+        <v>-4.583681772931548</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.102581209454323</v>
+        <v>1.124124802114301</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4315739415164391</v>
+        <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.699009570690804</v>
+        <v>2.757088204853823</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.654350052731995</v>
+        <v>-4.600491071082049</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.094937966934233</v>
+        <v>1.116481559594211</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4483832396669408</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.688004468540613</v>
+        <v>2.746083102703632</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.592052053955872</v>
+        <v>-4.538193072305927</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.186192720241502</v>
+        <v>1.20773631290148</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4483832396669408</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.754340022337434</v>
+        <v>2.812418656500453</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.390261856290715</v>
+        <v>-4.336402874640769</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9754896716969634</v>
+        <v>0.9970332643569417</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.2503650474977864</v>
+        <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.581731810028325</v>
+        <v>2.639810444191344</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.316883759201978</v>
+        <v>-4.263024777552033</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.075131142854633</v>
+        <v>1.096674735514611</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1769869504090498</v>
+        <v>-0.08018922680401847</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.696048900603742</v>
+        <v>2.754127534766761</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.414624303826953</v>
+        <v>-4.360765322177008</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.050662661120687</v>
+        <v>1.072206253780665</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.19287622854203</v>
+        <v>-0.09607850493699865</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.701143069839998</v>
+        <v>2.759221704003016</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.590962063949882</v>
+        <v>-4.537103082299937</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.978663537896187</v>
+        <v>1.000207130556165</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.3692139886649594</v>
+        <v>-0.2724162650599281</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.593876394590912</v>
+        <v>2.65195502875393</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397797</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.514540017517955</v>
+        <v>-4.46068103586801</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.007723974508886</v>
+        <v>1.029267567168864</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.3692139886649594</v>
+        <v>-0.2724162650599281</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.59236801263084</v>
+        <v>2.650446646793859</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024965</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.470166885879387</v>
+        <v>-4.416307904229441</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.02533609459975</v>
+        <v>1.046879687259728</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3248408570263908</v>
+        <v>-0.2280431334213595</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.618854759049418</v>
+        <v>2.676933393212436</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.462212915584614</v>
+        <v>-4.408353933934669</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.028517682717659</v>
+        <v>1.050061275377637</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3248408570263908</v>
+        <v>-0.2280431334213595</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.618854759049418</v>
+        <v>2.676933393212436</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.414557185023559</v>
+        <v>-4.360698203373613</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.053961731969886</v>
+        <v>1.075505324629864</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2771851264653352</v>
+        <v>-0.1803874028603038</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.653829954413855</v>
+        <v>2.711908588576875</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.286872875229262</v>
+        <v>-4.233013893579317</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.109927829262329</v>
+        <v>1.131471421922307</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1495008166710387</v>
+        <v>-0.05270309306600734</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.735332913665158</v>
+        <v>2.793411547828177</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.347539465631652</v>
+        <v>-4.293680483981706</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.072415865577246</v>
+        <v>1.093959458237224</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.2311991333895724</v>
+        <v>-0.134401409784541</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.673068596109911</v>
+        <v>2.731147230272929</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.302701064023253</v>
+        <v>-4.248842082373308</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.094448928831234</v>
+        <v>1.115992521491212</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.2266557004447029</v>
+        <v>-0.1298579768396715</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.679892358487461</v>
+        <v>2.737970992650479</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.403459699780251</v>
+        <v>-4.349600718130306</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.058306414159512</v>
+        <v>1.079850006819491</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.3154812691717083</v>
+        <v>-0.218683545566677</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.630757956882335</v>
+        <v>2.688836591045354</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.359256862694351</v>
+        <v>-4.305397881044406</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.08186715152171</v>
+        <v>1.103410744181688</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2712784320858079</v>
+        <v>-0.1744807084807765</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.663159261661713</v>
+        <v>2.721237895824732</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.396235890357794</v>
+        <v>-4.342376908707848</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.06548554092558</v>
+        <v>1.087029133585558</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.2343045302944773</v>
+        <v>-0.137506806689446</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.683753603205759</v>
+        <v>2.741832237368778</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.416293969222634</v>
+        <v>-4.362434987572689</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.108710074562683</v>
+        <v>1.130253667222662</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.2343045302944773</v>
+        <v>-0.137506806689446</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.735001368388798</v>
+        <v>2.793080002551817</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.376363296044744</v>
+        <v>-4.322504314394799</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.123123048428093</v>
+        <v>1.144666641088071</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.194373857116587</v>
+        <v>-0.09757613351155564</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.757400476889786</v>
+        <v>2.815479111052805</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.325331203322216</v>
+        <v>-4.271472221672271</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.138484113755374</v>
+        <v>1.160027706415352</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.143341764394059</v>
+        <v>-0.04654404078902769</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.782967960761572</v>
+        <v>2.841046594924591</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.260107022195011</v>
+        <v>-4.206248040545066</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.181761190298961</v>
+        <v>1.203304782958939</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.07811758326685342</v>
+        <v>0.01868014033817794</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.839289873530601</v>
+        <v>2.89736850769362</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.222680002123877</v>
+        <v>-4.168821020473931</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.192692970626695</v>
+        <v>1.214236563286673</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.07286604523767176</v>
+        <v>0.0239316783673596</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.83840176864739</v>
+        <v>2.896480402810409</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.242791658158585</v>
+        <v>-4.105787511438455</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.185905100544052</v>
+        <v>1.240706759232104</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.06183870024025256</v>
+        <v>0.0690559626676161</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.846274967977082</v>
+        <v>2.924811765721803</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82869047939355</v>
+        <v>3.828690479393549</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.18904684373138</v>
+        <v>-4.05204269701125</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.367960797336145</v>
+        <v>1.422762456024197</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.0517753907997906</v>
+        <v>0.07911927210807806</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.01287072466257</v>
+        <v>3.091407522407291</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.165255275125238</v>
+        <v>-4.028251128405108</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.497590333996419</v>
+        <v>1.552391992684471</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.02798382219364831</v>
+        <v>0.1029108407142204</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.147258575044072</v>
+        <v>3.225795372788794</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.13917119086143</v>
+        <v>-4.0021670441413</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.499731943715801</v>
+        <v>1.554533602403853</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.02798382219364831</v>
+        <v>0.1029108407142204</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.138966551057931</v>
+        <v>3.217503348802653</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.134836887804382</v>
+        <v>-3.997832741084252</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.4996588605224</v>
+        <v>1.554460519210452</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1236662811255556</v>
+        <v>0.2545609440334243</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.228149808633233</v>
+        <v>3.306686606377955</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.125944426411099</v>
+        <v>-3.988940279690969</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.520770250806504</v>
+        <v>1.575571909494556</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1236662811255556</v>
+        <v>0.2545609440334243</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.245704214360025</v>
+        <v>3.324241012104746</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.294420543380976</v>
+        <v>-4.157416396660846</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.445234851423137</v>
+        <v>1.500036510111189</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.09571844540897484</v>
+        <v>0.2266131083168435</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.22079056033466</v>
+        <v>3.299327358079381</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.596621014519393</v>
+        <v>-3.459616867799263</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.705624360155632</v>
+        <v>1.760426018843684</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.02537038603856412</v>
+        <v>0.1562650489464328</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.159851421900275</v>
+        <v>3.238388219644997</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.573899910836241</v>
+        <v>-3.43689576411611</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.705376824125798</v>
+        <v>1.76017848281385</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.02537038603856412</v>
+        <v>0.1562650489464328</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.15051544439718</v>
+        <v>3.229052242141901</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.572174867546197</v>
+        <v>-3.435170720826067</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.864972967292984</v>
+        <v>1.919774625981036</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.02709542932860787</v>
+        <v>0.1579900922364765</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.310456596222375</v>
+        <v>3.388993393967096</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.726955874324452</v>
+        <v>-3.589951727604322</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.840138387075329</v>
+        <v>1.894940045763381</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.006272244725868237</v>
+        <v>0.1246224181820004</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.327513814283336</v>
+        <v>3.406050612028058</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557223</v>
+        <v>3.769472653557224</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.794216318346369</v>
+        <v>-3.657212171626239</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.809909565456107</v>
+        <v>1.864711224144159</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.07353268874778535</v>
+        <v>0.05736197416008332</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.283832903859731</v>
+        <v>3.362369701604452</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088378</v>
+        <v>3.766702530088379</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.771744784307538</v>
+        <v>-3.634740637587407</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.828904332716381</v>
+        <v>1.883705991404434</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.06217279606818588</v>
+        <v>0.1930674589760545</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.375262348394056</v>
+        <v>3.453799146138777</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.907697792363853</v>
+        <v>-3.770693645643723</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.958626261638815</v>
+        <v>2.013427920326867</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.06217279606818588</v>
+        <v>0.1930674589760545</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.559365480539015</v>
+        <v>3.637902278283736</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,45 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.542999933995473</v>
+        <v>3.743954539471677</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.930105910168725</v>
+        <v>-3.793101763448595</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.941779709419859</v>
+        <v>1.996581368107911</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.06217279606818588</v>
+        <v>0.1930674589760545</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.551482175442009</v>
+        <v>3.63001897318673</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" s="2" t="n">
+        <v>45467</v>
+      </c>
+      <c r="B2005" t="n">
+        <v>3.825206488184731</v>
+      </c>
+      <c r="C2005" t="n">
+        <v>3.643072708287376</v>
+      </c>
+      <c r="D2005" t="n">
+        <v>-3.793101763448595</v>
+      </c>
+      <c r="E2005" t="n">
+        <v>1.996581368107911</v>
+      </c>
+      <c r="F2005" t="n">
+        <v>0.1930674589760545</v>
+      </c>
+      <c r="G2005" t="n">
+        <v>3.636136505273744</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240624.xlsx
+++ b/tame_output/ON/bt/strategyON_20240624.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.6%</t>
+          <t>-69.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-540.9%</t>
+          <t>-542.7%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>120.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.6%</t>
+          <t>-177.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-173.8%</t>
+          <t>-174.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-204.7%</t>
+          <t>-205.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-82.4%</t>
+          <t>-83.5%</t>
         </is>
       </c>
     </row>
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.131754021788826</v>
+        <v>-9.012728882024856</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5374527680912418</v>
+        <v>-0.4898427121856539</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.767985504692381</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.983398878264226</v>
+        <v>2.054813962122608</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.491284344292827</v>
+        <v>-9.372259204528858</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6759145937947921</v>
+        <v>-0.6283045378892043</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.767985504692381</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.988749181562276</v>
+        <v>2.060164265420657</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.541633407747049</v>
+        <v>-9.42260826798308</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6881381992193036</v>
+        <v>-0.6405281433137158</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.937359707910573</v>
+        <v>-1.818334568146603</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96645576344692</v>
+        <v>2.037870847305302</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.639252685168445</v>
+        <v>-9.520227545404476</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7241441595660931</v>
+        <v>-0.6765341036605053</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.03497898533197</v>
+        <v>-1.915953845568</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.91092594761585</v>
+        <v>1.982341031474233</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.786778773174088</v>
+        <v>-9.667753633410118</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7802610384467781</v>
+        <v>-0.7326509825411902</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.182505073337614</v>
+        <v>-2.063479933573644</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825303851134037</v>
+        <v>1.896718934992419</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.991036948503952</v>
+        <v>-9.872011808739982</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.856451111460081</v>
+        <v>-0.8088410555544931</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.310144017951603</v>
+        <v>-2.191118878187633</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>1.825648765342668</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.06536992476412</v>
+        <v>-9.946344785000147</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8817017474797111</v>
+        <v>-0.8340916915741228</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.454843541886275</v>
+        <v>-2.335818402122305</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.671896521607918</v>
+        <v>1.7433116054663</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.991900093096667</v>
+        <v>-9.872874953332698</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.83694211331931</v>
+        <v>-0.7893320574137221</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.381373710218827</v>
+        <v>-2.262348570454857</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731350122101808</v>
+        <v>1.80276520596019</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.16702451048321</v>
+        <v>-10.04799937071924</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8924366595264104</v>
+        <v>-0.844826603620823</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.437472987841401</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.640830692417399</v>
+        <v>1.712245776275781</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.4014766044977</v>
+        <v>-10.28245146473373</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9934366620338024</v>
+        <v>-0.945826606128215</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.437472987841401</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.633611527515803</v>
+        <v>1.705026611374185</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.50585133552415</v>
+        <v>-10.38682619576018</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.041858745218357</v>
+        <v>-0.9942486893127698</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.660872858631816</v>
+        <v>-2.541847718867846</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.564314498125959</v>
+        <v>1.635729581984341</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.55863749112447</v>
+        <v>-10.4396123513605</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.061857417619931</v>
+        <v>-1.014247361714344</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.756548345214213</v>
+        <v>-2.637523205450243</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.508024996015078</v>
+        <v>1.579440079873459</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.68467428449276</v>
+        <v>-10.56564914472879</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.109578406338132</v>
+        <v>-1.061968350432545</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.612271582640501</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.525869698330037</v>
+        <v>1.59728478218842</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.63265877052395</v>
+        <v>-10.51363363075998</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.084781865064206</v>
+        <v>-1.037171809158619</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.612271582640501</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.529860034016438</v>
+        <v>1.60127511787482</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.77433061224807</v>
+        <v>-10.6553054724841</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.142925828652596</v>
+        <v>-1.095315772747009</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.612271582640501</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.528384807117697</v>
+        <v>1.599799890976079</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.72473976782324</v>
+        <v>-10.60571462805927</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.10803608071779</v>
+        <v>-1.060426024812202</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.681705877979637</v>
+        <v>-2.562680738215667</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.573192723937469</v>
+        <v>1.644607807795851</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.71193237481846</v>
+        <v>-10.59290723505449</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.115964257162564</v>
+        <v>-1.068354201256976</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.730561652988538</v>
+        <v>-2.611536513224568</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.530828125285446</v>
+        <v>1.602243209143827</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.48608722209905</v>
+        <v>-10.36706208233508</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.016047123038591</v>
+        <v>-0.9684370671330034</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.569609837637405</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.565563203673952</v>
+        <v>1.636978287532334</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.36150856576146</v>
+        <v>-10.24248342599749</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9650765159474957</v>
+        <v>-0.9174664600419074</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.569609837637405</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.566702348230011</v>
+        <v>1.638117432088393</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.41440385380575</v>
+        <v>-10.29537871404178</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9836008570031023</v>
+        <v>-0.9359908010975149</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.564654491548958</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.572309330045187</v>
+        <v>1.643724413903569</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.34227067851787</v>
+        <v>-10.2232455387539</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9490138826493135</v>
+        <v>-0.9014038267437252</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.564654491548958</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.578043034283823</v>
+        <v>1.649458118142205</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.27090428590822</v>
+        <v>-10.15187914614425</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9302045879993202</v>
+        <v>-0.8825945320937318</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.49328809893931</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.611125607455747</v>
+        <v>1.682540691314129</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17744525192299</v>
+        <v>-10.05842011215902</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9027044557181374</v>
+        <v>-0.85509439981255</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.49328809893931</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.601242126142839</v>
+        <v>1.672657210001221</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.910203451054596</v>
+        <v>-9.791178311290626</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7976422958701521</v>
+        <v>-0.7500322399645643</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.49328809893931</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.599407565643466</v>
+        <v>1.670822649501847</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.812296412378105</v>
+        <v>-9.693271272614135</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7587797953730169</v>
+        <v>-0.711169739467429</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.544327488842724</v>
+        <v>-2.425302349078754</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.639898700586339</v>
+        <v>1.711313784444721</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.788342871402147</v>
+        <v>-9.669317731638177</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7485298728371399</v>
+        <v>-0.700919816931552</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.520373947866766</v>
+        <v>-2.401348808102796</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.654939331317407</v>
+        <v>1.726354415175789</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.52428293307935</v>
+        <v>-9.40525779331538</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6561662136697732</v>
+        <v>-0.6085561577641854</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.13728886978</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.800114978149332</v>
+        <v>1.871530062007714</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.817203309574513</v>
+        <v>-8.698178169810543</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3761213979281393</v>
+        <v>-0.3285113420225514</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.13728886978</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.797327944489031</v>
+        <v>1.868743028347413</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.777019011208322</v>
+        <v>-8.657993871444353</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3597040546938217</v>
+        <v>-0.3120939987882339</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.216129711177779</v>
+        <v>-2.097104571413809</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.821782147396587</v>
+        <v>1.893197231254969</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626476</v>
+        <v>3.856161751626477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.613619140268959</v>
+        <v>-8.494594000504989</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2949772850973194</v>
+        <v>-0.2473672291917315</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.052729840238417</v>
+        <v>-1.933704700474447</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919188891180962</v>
+        <v>1.990603975039344</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.38013791803936</v>
+        <v>-8.26111277827539</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1936603673676274</v>
+        <v>-0.1460503114620395</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.819248618008818</v>
+        <v>-1.700223478244848</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.067202053356573</v>
+        <v>2.138617137214955</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.230471527031845</v>
+        <v>-8.111446387267875</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1366860212775807</v>
+        <v>-0.0890759653719928</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.726345126766282</v>
+        <v>-1.607319987002312</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.120051937789135</v>
+        <v>2.191467021647517</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.098196053400958</v>
+        <v>-7.979170913636989</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08840834507819872</v>
+        <v>-0.0407982891726113</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.594069653135396</v>
+        <v>-1.475044513371426</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.194784708714694</v>
+        <v>2.266199792573076</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.942457720841216</v>
+        <v>-7.823432581077247</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02329795136666535</v>
+        <v>0.02431210453892207</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.319306180811684</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.291042768938176</v>
+        <v>2.362457852796558</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.693457922157635</v>
+        <v>-7.574432782393666</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08920830933042589</v>
+        <v>0.1368183652360133</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.319306180811684</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.303949110161835</v>
+        <v>2.375364194020217</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.79904791193074</v>
+        <v>-7.680022772166771</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08100361617803475</v>
+        <v>-0.03339356027244733</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.543921310348759</v>
+        <v>-1.424896170584789</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.112619186698754</v>
+        <v>2.184034270557135</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.817782814049337</v>
+        <v>-7.698757674285368</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03995323514838711</v>
+        <v>0.007656820757200311</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.54951732000889</v>
+        <v>-1.43049218024492</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.157805922779761</v>
+        <v>2.229221006638143</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.669842772641737</v>
+        <v>-7.550817632877768</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.100656141273515</v>
+        <v>-0.05304608536792754</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.529196404100332</v>
+        <v>-1.410171264336362</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.050119549636728</v>
+        <v>2.12153463349511</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.616873250387749</v>
+        <v>-7.49784811062378</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08818231862539783</v>
+        <v>-0.0405722627198104</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.357201742082374</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.073187276735643</v>
+        <v>2.144602360594025</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.573324843617058</v>
+        <v>-7.454299703853089</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07772356801221481</v>
+        <v>-0.03011351210662738</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.357201742082374</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.06622666464055</v>
+        <v>2.137641748498932</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.3311764501632</v>
+        <v>-7.212151310399231</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03359814375047154</v>
+        <v>0.08120819965605897</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.357201742082374</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.080689019021693</v>
+        <v>2.152104102880075</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.222917313040679</v>
+        <v>-7.10389217327671</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07143391905867524</v>
+        <v>0.1190439749642627</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.357201742082374</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.075221139480888</v>
+        <v>2.14663622333927</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.099626178223548</v>
+        <v>-6.980601038459579</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1182484669961044</v>
+        <v>0.1658585229016922</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.352935747029213</v>
+        <v>-1.233910607265243</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.146693914381743</v>
+        <v>2.218108998240125</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.078476979320104</v>
+        <v>-6.959451839556135</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1344091247948072</v>
+        <v>0.1820191807003946</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.2127614083618</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.167084411961135</v>
+        <v>2.238499495819517</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.83471153733666</v>
+        <v>-6.715686397572691</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2276960099352352</v>
+        <v>0.2753060658408231</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.2127614083618</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.162865120308185</v>
+        <v>2.234280204166567</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.732948717059365</v>
+        <v>-6.613923577295396</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2705254519661695</v>
+        <v>0.3181355078717569</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.199542339969371</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.172920875263658</v>
+        <v>2.24433595912204</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.483098323110291</v>
+        <v>-6.364073183346322</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3632076845295011</v>
+        <v>0.410817740435089</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.199542339969371</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.165662950247361</v>
+        <v>2.237078034105743</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.307206230642858</v>
+        <v>-6.188181090878889</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4371636450371228</v>
+        <v>0.4847737009427107</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.199542339969371</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.169262073768009</v>
+        <v>2.240677157626391</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.135759767620395</v>
+        <v>-6.016734627856425</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5190697363006618</v>
+        <v>0.5666797922062501</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.147121016710878</v>
+        <v>-1.028095876946908</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.285457457636041</v>
+        <v>2.356872541494423</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.061470201882056</v>
+        <v>-5.942445062118086</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5478060402122944</v>
+        <v>0.5954160961178827</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.072831450972539</v>
+        <v>-0.9538063112085686</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.329051674695342</v>
+        <v>2.400466758553724</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.997834459648121</v>
+        <v>-5.878809319884152</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5779551381601857</v>
+        <v>0.6255651940657736</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.8901705689746341</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.37192792109002</v>
+        <v>2.443343004948401</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.886407700322201</v>
+        <v>-5.767382560558231</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6037201006743493</v>
+        <v>0.6513301565799372</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.8901705689746341</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.353122179873815</v>
+        <v>2.424537263732197</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.645977203517341</v>
+        <v>-5.526952063753371</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7016353760211711</v>
+        <v>0.749245431926759</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.6497400721697738</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.499123554581609</v>
+        <v>2.570538638439991</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.573734635346146</v>
+        <v>-5.454709495582176</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7344617171244692</v>
+        <v>0.782071773030057</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.6497400721697738</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.503052868416429</v>
+        <v>2.574467952274811</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.520736313064758</v>
+        <v>-5.401711173300789</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7563396299543643</v>
+        <v>0.8039496858599522</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.594403813167835</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.536933207734932</v>
+        <v>2.608348291593314</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.411931427585031</v>
+        <v>-5.292906287821062</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7968596553662484</v>
+        <v>0.8444697112718362</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.594403813167835</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.533931278954926</v>
+        <v>2.605346362813308</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.191910629548021</v>
+        <v>-5.126744471433997</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8864470115916667</v>
+        <v>0.9125134748372763</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.5499816917048862</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620242223006328</v>
+        <v>2.633578672701691</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.059042940484743</v>
+        <v>-4.99387678237072</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.955488270018801</v>
+        <v>0.9815547332644106</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.5499816917048862</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636136405808151</v>
+        <v>2.649472855503515</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.938869857120245</v>
+        <v>-4.873703699006221</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.004703347804903</v>
+        <v>1.030769811050512</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4520360244993256</v>
+        <v>-0.4298086083403873</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.709386100267153</v>
+        <v>2.722722549962516</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.794197712020507</v>
+        <v>-4.729031553906483</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.072660308406237</v>
+        <v>1.098726771651847</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3073638793995881</v>
+        <v>-0.2851364632406498</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.806277489888435</v>
+        <v>2.819613939583798</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.854072539378199</v>
+        <v>-4.788906381264176</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.034747868864586</v>
+        <v>1.060814332110196</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.345011290598342</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.756390084875245</v>
+        <v>2.769726534570609</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.767273041599191</v>
+        <v>-4.702106883485166</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.091868161298756</v>
+        <v>1.117934624544366</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.345011290598342</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.778790578197811</v>
+        <v>2.792127027893175</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.769742748060997</v>
+        <v>-4.704576589946972</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.090952680087445</v>
+        <v>1.117019143333055</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3697084132190864</v>
+        <v>-0.3474809970601481</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.77738115569414</v>
+        <v>2.790717605389503</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.838112934385007</v>
+        <v>-4.772946776270983</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074611528032543</v>
+        <v>1.100677991278153</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3382052980239332</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.793953497590571</v>
+        <v>2.807289947285934</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.851900987232054</v>
+        <v>-4.786734829118029</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.059533015525616</v>
+        <v>1.085599478771226</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3382052980239332</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.784390206222462</v>
+        <v>2.797726655917825</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.882894146560759</v>
+        <v>-4.817727988446735</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8718453168345206</v>
+        <v>0.8979117800801304</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3382052980239332</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.609099771262849</v>
+        <v>2.622436220958212</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.707419886768291</v>
+        <v>-4.642253728654266</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.946602252743296</v>
+        <v>0.9726687159889058</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3382052980239332</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.613667003254637</v>
+        <v>2.62700345295</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.81835613940954</v>
+        <v>-4.753189981295515</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8779697804480033</v>
+        <v>0.9040362436936134</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3382052980239332</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.589409032015844</v>
+        <v>2.602745481711207</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.784692593937257</v>
+        <v>-4.719526435823233</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8945665838568218</v>
+        <v>0.9206330471024318</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.3045417525516513</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.612738544519118</v>
+        <v>2.626074994214481</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.724839974733534</v>
+        <v>-4.65967381661951</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9286800179704435</v>
+        <v>0.9547464812160533</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.3045417525516513</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.622910930951251</v>
+        <v>2.636247380646614</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.638596511707156</v>
+        <v>-4.573430353593132</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9581236737548549</v>
+        <v>0.9841901370004646</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.3045417525516513</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.617857201525111</v>
+        <v>2.631193651220474</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.683903331106136</v>
+        <v>-4.618737172992112</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9317767214397885</v>
+        <v>0.9578431846853983</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.3453519155608821</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.585146879164098</v>
+        <v>2.598483328859461</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.712936435808437</v>
+        <v>-4.647770277694413</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9207153525919696</v>
+        <v>0.9467818158375794</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.3453519155608821</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.5856987521972</v>
+        <v>2.599035201892563</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.620125954357578</v>
+        <v>-4.554959796243553</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.887112237063679</v>
+        <v>0.913178700309289</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2747688502689611</v>
+        <v>-0.2525414341100228</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.570657732959081</v>
+        <v>2.583994182654444</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.664515423687005</v>
+        <v>-4.599349265572981</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.871229925256509</v>
+        <v>0.8972963885021188</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3191583195983888</v>
+        <v>-0.2969309034394504</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.545897527286025</v>
+        <v>2.559233976981388</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.551844205450755</v>
+        <v>-4.48667804733673</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.911374121062732</v>
+        <v>0.9374405843083418</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.1842596852032002</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.608575966739498</v>
+        <v>2.621912416434861</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.439467204268082</v>
+        <v>-4.374301046154057</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9618162173664684</v>
+        <v>0.9878826806120782</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.1842596852032002</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.614067262570166</v>
+        <v>2.627403712265528</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.467247602169435</v>
+        <v>-4.40208144405541</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9622012599744665</v>
+        <v>0.9882677232200763</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2342674992634916</v>
+        <v>-0.2120400831045533</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608896225597893</v>
+        <v>2.622232675293256</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.550248883194714</v>
+        <v>-4.485082725080689</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7673564675650082</v>
+        <v>0.793422930810618</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.2306109676317271</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.436109414882242</v>
+        <v>2.449445864577605</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.658862961638045</v>
+        <v>-4.59369680352402</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8440604969068812</v>
+        <v>0.8701269601524912</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.2306109676317271</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556259075601448</v>
+        <v>2.569595525296811</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.623453923389902</v>
+        <v>-4.558287765275877</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8727371383084614</v>
+        <v>0.8988036015540712</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.2306109676317271</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570772101703771</v>
+        <v>2.584108551399134</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.585070260831751</v>
+        <v>-4.519904102717726</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8855100446740907</v>
+        <v>0.9115765079197005</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.1922273050735759</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.59122174058103</v>
+        <v>2.604558190276393</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.407953930796585</v>
+        <v>-4.34278777268256</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9530856055334589</v>
+        <v>0.9791520687790687</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.1922273050735759</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587950769426332</v>
+        <v>2.601287219121695</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793906</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.45304617563013</v>
+        <v>-4.387880017516106</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9357320993619538</v>
+        <v>0.9617985626075636</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.276350764401904</v>
+        <v>-0.2541233482429657</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.551496535286611</v>
+        <v>2.564832984981974</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011239</v>
+        <v>3.750729377011237</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.273670754391363</v>
+        <v>-4.208504596277338</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.001269243163875</v>
+        <v>1.027335706409485</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1195740062311853</v>
+        <v>-0.097346590072247</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.639349565495456</v>
+        <v>2.65268601519082</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982233</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.318684967911969</v>
+        <v>-4.253518809797944</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9640710130872225</v>
+        <v>0.9901374763328326</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1499229015457899</v>
+        <v>-0.1276954853868516</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.601947683638284</v>
+        <v>2.615284133333647</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.585689478184404</v>
+        <v>-4.520523320070379</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8629607713171943</v>
+        <v>0.8890272345628043</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3442859395887385</v>
+        <v>-0.3220585234298002</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.49102142315146</v>
+        <v>2.504357872846823</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.686887259621576</v>
+        <v>-4.621721101507552</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8216855806388268</v>
+        <v>0.8477520438844366</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.3904673369751194</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.44918005692077</v>
+        <v>2.462516506616133</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.654411673450804</v>
+        <v>-4.589245515336779</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8322757766614524</v>
+        <v>0.8583422399070622</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.3904673369751194</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.446780018475087</v>
+        <v>2.46011646817045</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.635373545743507</v>
+        <v>-4.570207387629482</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8364157469526161</v>
+        <v>0.8624822101982259</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.4486509483063139</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.408394570884615</v>
+        <v>2.421731020579978</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.666500176894125</v>
+        <v>-4.601334018780101</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.001546963431049</v>
+        <v>1.027613426676659</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.4486509483063139</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.585976439823296</v>
+        <v>2.599312889518659</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067869</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.680366938228043</v>
+        <v>-4.615200780114018</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9968335878836156</v>
+        <v>1.022900051129226</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.4865088650401369</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564095018769136</v>
+        <v>2.577431468464499</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.635562766688113</v>
+        <v>-4.570396608574089</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.020763786896514</v>
+        <v>1.046830250142123</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.4865088650401369</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570103549166062</v>
+        <v>2.583439998861425</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.487819796453111</v>
+        <v>-4.422653638339086</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.159013622782537</v>
+        <v>1.185080086028147</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.3187015078052537</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.749940611299013</v>
+        <v>2.763277060994376</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181174</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.589834478984332</v>
+        <v>-4.524668320870307</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.121001371301529</v>
+        <v>1.147067834547139</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.3187015078052537</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752734232830494</v>
+        <v>2.766070682525857</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.583681772931548</v>
+        <v>-4.518515614817523</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.124124802114301</v>
+        <v>1.150191265359911</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3347762179114078</v>
+        <v>-0.3125488017524694</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.757088204853823</v>
+        <v>2.770424654549186</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.600491071082049</v>
+        <v>-4.535324912968025</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.116481559594211</v>
+        <v>1.14254802283982</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.329358099902971</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746083102703632</v>
+        <v>2.759419552398995</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.538193072305927</v>
+        <v>-4.473026914191903</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.20773631290148</v>
+        <v>1.23380277614709</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.329358099902971</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.812418656500453</v>
+        <v>2.825755106195816</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992195</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.336402874640769</v>
+        <v>-4.271236716526745</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9970332643569417</v>
+        <v>1.023099727602552</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.153567323892755</v>
+        <v>-0.1313399077338167</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.639810444191344</v>
+        <v>2.653146893886707</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.263024777552033</v>
+        <v>-4.197858619438009</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.096674735514611</v>
+        <v>1.122741198760221</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.08018922680401847</v>
+        <v>-0.0579618106450801</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.754127534766761</v>
+        <v>2.767463984462124</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319549</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.360765322177008</v>
+        <v>-4.295599164062983</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.072206253780665</v>
+        <v>1.098272717026275</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.09607850493699865</v>
+        <v>-0.07385108877806029</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.759221704003016</v>
+        <v>2.772558153698379</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.537103082299937</v>
+        <v>-4.471936924185912</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.000207130556165</v>
+        <v>1.026273593801775</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2724162650599281</v>
+        <v>-0.2501888489009897</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.65195502875393</v>
+        <v>2.665291478449293</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397797</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.46068103586801</v>
+        <v>-4.395514877753985</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.029267567168864</v>
+        <v>1.055334030414474</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2724162650599281</v>
+        <v>-0.2501888489009897</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.650446646793859</v>
+        <v>2.663783096489222</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024965</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.416307904229441</v>
+        <v>-4.351141746115417</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.046879687259728</v>
+        <v>1.072946150505338</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2280431334213595</v>
+        <v>-0.2058157172624211</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.676933393212436</v>
+        <v>2.690269842907799</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.408353933934669</v>
+        <v>-4.343187775820645</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.050061275377637</v>
+        <v>1.076127738623247</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2280431334213595</v>
+        <v>-0.2058157172624211</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.676933393212436</v>
+        <v>2.690269842907799</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.360698203373613</v>
+        <v>-4.295532045259589</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.075505324629864</v>
+        <v>1.101571787875474</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1803874028603038</v>
+        <v>-0.1581599867013654</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.711908588576875</v>
+        <v>2.725245038272238</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.233013893579317</v>
+        <v>-4.167847735465292</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.131471421922307</v>
+        <v>1.157537885167917</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.05270309306600734</v>
+        <v>-0.03047567690706898</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.793411547828177</v>
+        <v>2.80674799752354</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.82883791131455</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.293680483981706</v>
+        <v>-4.228514325867682</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.093959458237224</v>
+        <v>1.120025921482834</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.134401409784541</v>
+        <v>-0.1121739936256027</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.731147230272929</v>
+        <v>2.744483679968292</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.248842082373308</v>
+        <v>-4.183675924259283</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.115992521491212</v>
+        <v>1.142058984736821</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1298579768396715</v>
+        <v>-0.1076305606807332</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.737970992650479</v>
+        <v>2.751307442345842</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.349600718130306</v>
+        <v>-4.284434560016281</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.079850006819491</v>
+        <v>1.1059164700651</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.218683545566677</v>
+        <v>-0.1964561294077386</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.688836591045354</v>
+        <v>2.702173040740717</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163221</v>
+        <v>3.826713779163219</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.305397881044406</v>
+        <v>-4.240231722930381</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.103410744181688</v>
+        <v>1.129477207427298</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1744807084807765</v>
+        <v>-0.1522532923218382</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.721237895824732</v>
+        <v>2.734574345520095</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.342376908707848</v>
+        <v>-4.277210750593824</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.087029133585558</v>
+        <v>1.113095596831168</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.137506806689446</v>
+        <v>-0.1152793905305076</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.741832237368778</v>
+        <v>2.755168687064141</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.362434987572689</v>
+        <v>-4.297268829458664</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.130253667222662</v>
+        <v>1.156320130468272</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.137506806689446</v>
+        <v>-0.1152793905305076</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.793080002551817</v>
+        <v>2.80641645224718</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.322504314394799</v>
+        <v>-4.257338156280774</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.144666641088071</v>
+        <v>1.170733104333681</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.09757613351155564</v>
+        <v>-0.07534871735261728</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.815479111052805</v>
+        <v>2.828815560748168</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.271472221672271</v>
+        <v>-4.206306063558246</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.160027706415352</v>
+        <v>1.186094169660962</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.04654404078902769</v>
+        <v>-0.02431662463008932</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.841046594924591</v>
+        <v>2.854383044619954</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.206248040545066</v>
+        <v>-4.141081882431041</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.203304782958939</v>
+        <v>1.229371246204549</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.01868014033817794</v>
+        <v>0.0409075564971163</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.89736850769362</v>
+        <v>2.910704957388983</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639817</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.168821020473931</v>
+        <v>-4.103654862359907</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.214236563286673</v>
+        <v>1.240303026532283</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.0239316783673596</v>
+        <v>0.04615909452629796</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.896480402810409</v>
+        <v>2.909816852505772</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749923</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.105787511438455</v>
+        <v>-4.123766518394615</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.240706759232104</v>
+        <v>1.23351515644964</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0690559626676161</v>
+        <v>0.05718643952371716</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.924811765721803</v>
+        <v>2.917690051835464</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393549</v>
+        <v>3.828690479393548</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.05204269701125</v>
+        <v>-4.07002170396741</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.422762456024197</v>
+        <v>1.415570853241733</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.07911927210807806</v>
+        <v>0.06724974896417912</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.091407522407291</v>
+        <v>3.084285808520952</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714887</v>
+        <v>3.813251854714886</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.028251128405108</v>
+        <v>-4.046230135361268</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.552391992684471</v>
+        <v>1.545200389902007</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1029108407142204</v>
+        <v>0.09104131757032141</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.225795372788794</v>
+        <v>3.218673658902454</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756013</v>
+        <v>3.814259761756011</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.0021670441413</v>
+        <v>-4.02014605109746</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.554533602403853</v>
+        <v>1.547341999621389</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1029108407142204</v>
+        <v>0.09104131757032141</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.217503348802653</v>
+        <v>3.210381634916313</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654187</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.997832741084252</v>
+        <v>-4.015811748040412</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.554460519210452</v>
+        <v>1.547268916427988</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2545609440334243</v>
+        <v>0.2426914208895253</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.306686606377955</v>
+        <v>3.299564892491615</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717118</v>
+        <v>3.796293177717116</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.988940279690969</v>
+        <v>-4.006919286647129</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.575571909494556</v>
+        <v>1.568380306712092</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2545609440334243</v>
+        <v>0.2426914208895253</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.324241012104746</v>
+        <v>3.317119298218406</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702627</v>
+        <v>3.794453975702625</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.157416396660846</v>
+        <v>-4.175395403617006</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.500036510111189</v>
+        <v>1.492844907328725</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2266131083168435</v>
+        <v>0.2147435851729446</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.299327358079381</v>
+        <v>3.292205644193042</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539967</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.459616867799263</v>
+        <v>-3.477595874755423</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.760426018843684</v>
+        <v>1.75323441606122</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1562650489464328</v>
+        <v>0.1443955258025338</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.238388219644997</v>
+        <v>3.231266505758657</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389899</v>
+        <v>3.784700379389897</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.43689576411611</v>
+        <v>-3.454874771072271</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.76017848281385</v>
+        <v>1.752986880031386</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1562650489464328</v>
+        <v>0.1443955258025338</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.229052242141901</v>
+        <v>3.221930528255562</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534937</v>
+        <v>3.783234730534935</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.435170720826067</v>
+        <v>-3.453149727782227</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.919774625981036</v>
+        <v>1.912583023198572</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1579900922364765</v>
+        <v>0.1461205690925776</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.388993393967096</v>
+        <v>3.381871680080757</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401675</v>
+        <v>3.779962759401674</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.589951727604322</v>
+        <v>-3.607930734560482</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.894940045763381</v>
+        <v>1.887748442980917</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1246224181820004</v>
+        <v>0.1127528950381015</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.406050612028058</v>
+        <v>3.398928898141718</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557224</v>
+        <v>3.769472653557222</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.657212171626239</v>
+        <v>-3.675191178582399</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.864711224144159</v>
+        <v>1.857519621361695</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.05736197416008332</v>
+        <v>0.04549245101618438</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.362369701604452</v>
+        <v>3.355247987718113</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088379</v>
+        <v>3.766702530088377</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.634740637587407</v>
+        <v>-3.652719644543568</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.883705991404434</v>
+        <v>1.876514388621969</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1930674589760545</v>
+        <v>0.1811979358321556</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.453799146138777</v>
+        <v>3.446677432252437</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541371</v>
+        <v>3.76808110154137</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.770693645643723</v>
+        <v>-3.788672652599884</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.013427920326867</v>
+        <v>2.006236317544403</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1930674589760545</v>
+        <v>0.1811979358321556</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.637902278283736</v>
+        <v>3.630780564397397</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.793101763448595</v>
+        <v>-3.811080770404756</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.996581368107911</v>
+        <v>1.989389765325447</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1930674589760545</v>
+        <v>0.1811979358321556</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.63001897318673</v>
+        <v>3.62289725930039</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.825206488184731</v>
+        <v>3.816337696227745</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.643072708287376</v>
+        <v>3.631821550827503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.793101763448595</v>
+        <v>-3.811080770404756</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.996581368107911</v>
+        <v>1.989389765325447</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1930674589760545</v>
+        <v>0.1811979358321556</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.636136505273744</v>
+        <v>3.624885347813871</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240624.xlsx
+++ b/tame_output/ON/bt/strategyON_20240624.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>28.8%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>36.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.4%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.5%</t>
+          <t>-67.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.1%</t>
+          <t>457.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-542.7%</t>
+          <t>-501.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>114.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-177.3%</t>
+          <t>-160.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-174.6%</t>
+          <t>-156.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-205.9%</t>
+          <t>-174.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-83.5%</t>
+          <t>-98.6%</t>
         </is>
       </c>
     </row>
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.012728882024856</v>
+        <v>-9.131754021788826</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4898427121856539</v>
+        <v>-0.5374527680912418</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.767985504692381</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.054813962122608</v>
+        <v>1.983398878264226</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.372259204528858</v>
+        <v>-9.491284344292827</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6283045378892043</v>
+        <v>-0.6759145937947921</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.767985504692381</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.060164265420657</v>
+        <v>1.988749181562276</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.42260826798308</v>
+        <v>-9.541633407747049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6405281433137158</v>
+        <v>-0.6881381992193036</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.818334568146603</v>
+        <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.037870847305302</v>
+        <v>1.96645576344692</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.520227545404476</v>
+        <v>-9.639252685168445</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6765341036605053</v>
+        <v>-0.7241441595660931</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.915953845568</v>
+        <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.982341031474233</v>
+        <v>1.91092594761585</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.667753633410118</v>
+        <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7326509825411902</v>
+        <v>-0.7802610384467781</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.063479933573644</v>
+        <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.896718934992419</v>
+        <v>1.825303851134037</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.872011808739982</v>
+        <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8088410555544931</v>
+        <v>-0.856451111460081</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.191118878187633</v>
+        <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.825648765342668</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.946344785000147</v>
+        <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8340916915741228</v>
+        <v>-0.8817017474797111</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.335818402122305</v>
+        <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.7433116054663</v>
+        <v>1.671896521607918</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.872874953332698</v>
+        <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7893320574137221</v>
+        <v>-0.83694211331931</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.262348570454857</v>
+        <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.80276520596019</v>
+        <v>1.731350122101808</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.04799937071924</v>
+        <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.844826603620823</v>
+        <v>-0.8924366595264104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.437472987841401</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.712245776275781</v>
+        <v>1.640830692417399</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.28245146473373</v>
+        <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.945826606128215</v>
+        <v>-0.9934366620338024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.437472987841401</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.705026611374185</v>
+        <v>1.633611527515803</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.38682619576018</v>
+        <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9942486893127698</v>
+        <v>-1.041858745218357</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.541847718867846</v>
+        <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.635729581984341</v>
+        <v>1.564314498125959</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.4396123513605</v>
+        <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.014247361714344</v>
+        <v>-1.061857417619931</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.637523205450243</v>
+        <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.579440079873459</v>
+        <v>1.508024996015078</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.56564914472879</v>
+        <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.061968350432545</v>
+        <v>-1.109578406338132</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.612271582640501</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.59728478218842</v>
+        <v>1.525869698330037</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.51363363075998</v>
+        <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.037171809158619</v>
+        <v>-1.084781865064206</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.612271582640501</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.60127511787482</v>
+        <v>1.529860034016438</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.6553054724841</v>
+        <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.095315772747009</v>
+        <v>-1.142925828652596</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.612271582640501</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.599799890976079</v>
+        <v>1.528384807117697</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.60571462805927</v>
+        <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.060426024812202</v>
+        <v>-1.10803608071779</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.562680738215667</v>
+        <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.644607807795851</v>
+        <v>1.573192723937469</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.59290723505449</v>
+        <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.068354201256976</v>
+        <v>-1.115964257162564</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.611536513224568</v>
+        <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.602243209143827</v>
+        <v>1.530828125285446</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.36706208233508</v>
+        <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9684370671330034</v>
+        <v>-1.016047123038591</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.569609837637405</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.636978287532334</v>
+        <v>1.565563203673952</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.24248342599749</v>
+        <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9174664600419074</v>
+        <v>-0.9650765159474957</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.569609837637405</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.638117432088393</v>
+        <v>1.566702348230011</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.29537871404178</v>
+        <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9359908010975149</v>
+        <v>-0.9836008570031023</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.564654491548958</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.643724413903569</v>
+        <v>1.572309330045187</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.2232455387539</v>
+        <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9014038267437252</v>
+        <v>-0.9490138826493135</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.564654491548958</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.649458118142205</v>
+        <v>1.578043034283823</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.15187914614425</v>
+        <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8825945320937318</v>
+        <v>-0.9302045879993202</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.49328809893931</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.682540691314129</v>
+        <v>1.611125607455747</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.05842011215902</v>
+        <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.85509439981255</v>
+        <v>-0.9027044557181374</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.49328809893931</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.672657210001221</v>
+        <v>1.601242126142839</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.791178311290626</v>
+        <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7500322399645643</v>
+        <v>-0.7976422958701521</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.49328809893931</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.670822649501847</v>
+        <v>1.599407565643466</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.693271272614135</v>
+        <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.711169739467429</v>
+        <v>-0.7587797953730169</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.425302349078754</v>
+        <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.711313784444721</v>
+        <v>1.639898700586339</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.669317731638177</v>
+        <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.700919816931552</v>
+        <v>-0.7485298728371399</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.401348808102796</v>
+        <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.726354415175789</v>
+        <v>1.654939331317407</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017773</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.40525779331538</v>
+        <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6085561577641854</v>
+        <v>-0.6561662136697732</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.13728886978</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.871530062007714</v>
+        <v>1.800114978149332</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.698178169810543</v>
+        <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3285113420225514</v>
+        <v>-0.3761213979281393</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.13728886978</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.868743028347413</v>
+        <v>1.797327944489031</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388731</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.657993871444353</v>
+        <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3120939987882339</v>
+        <v>-0.3597040546938217</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.097104571413809</v>
+        <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.893197231254969</v>
+        <v>1.821782147396587</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626477</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.494594000504989</v>
+        <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2473672291917315</v>
+        <v>-0.2949772850973194</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.933704700474447</v>
+        <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.990603975039344</v>
+        <v>1.919188891180962</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.26111277827539</v>
+        <v>-8.37282720891432</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1460503114620395</v>
+        <v>-0.1907360837176113</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.700223478244848</v>
+        <v>-1.811937908883778</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.138617137214955</v>
+        <v>2.071588478831598</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.111446387267875</v>
+        <v>-8.223160817906805</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.0890759653719928</v>
+        <v>-0.133761737627565</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.607319987002312</v>
+        <v>-1.719034417641242</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.191467021647517</v>
+        <v>2.12443836326416</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.979170913636989</v>
+        <v>-8.090885344275918</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.0407982891726113</v>
+        <v>-0.0854840614281831</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.475044513371426</v>
+        <v>-1.586758944010355</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.266199792573076</v>
+        <v>2.199171134189719</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.823432581077247</v>
+        <v>-7.935147011716176</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.02431210453892207</v>
+        <v>-0.02037366771664928</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.319306180811684</v>
+        <v>-1.431020611450613</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.362457852796558</v>
+        <v>2.295429194413201</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.574432782393666</v>
+        <v>-7.686147213032595</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1368183652360133</v>
+        <v>0.09213259298044152</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.319306180811684</v>
+        <v>-1.431020611450613</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.375364194020217</v>
+        <v>2.308335535636859</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.680022772166771</v>
+        <v>-7.7917372028057</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03339356027244733</v>
+        <v>-0.07807933252801869</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.424896170584789</v>
+        <v>-1.536610601223718</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.184034270557135</v>
+        <v>2.117005612173778</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.698757674285368</v>
+        <v>-7.810472104924297</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.007656820757200311</v>
+        <v>-0.03702895149837104</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.43049218024492</v>
+        <v>-1.542206610883849</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.229221006638143</v>
+        <v>2.162192348254786</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.550817632877768</v>
+        <v>-7.662532063516697</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05304608536792754</v>
+        <v>-0.0977318576234989</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.410171264336362</v>
+        <v>-1.521885694975291</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.12153463349511</v>
+        <v>2.054505975111753</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.49784811062378</v>
+        <v>-7.609562541262709</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.0405722627198104</v>
+        <v>-0.08525803497538176</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.357201742082374</v>
+        <v>-1.468916172721303</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.144602360594025</v>
+        <v>2.077573702210668</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.454299703853089</v>
+        <v>-7.566014134492018</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.03011351210662738</v>
+        <v>-0.07479928436219874</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.357201742082374</v>
+        <v>-1.468916172721303</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.137641748498932</v>
+        <v>2.070613090115574</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.212151310399231</v>
+        <v>-7.32386574103816</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.08120819965605897</v>
+        <v>0.03652242740048761</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.357201742082374</v>
+        <v>-1.468916172721303</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.152104102880075</v>
+        <v>2.085075444496717</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.10389217327671</v>
+        <v>-7.215606603915639</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1190439749642627</v>
+        <v>0.07435820270869131</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.357201742082374</v>
+        <v>-1.468916172721303</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.14663622333927</v>
+        <v>2.079607564955912</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.980601038459579</v>
+        <v>-7.092315469098508</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1658585229016922</v>
+        <v>0.1211727506461204</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.233910607265243</v>
+        <v>-1.345625037904172</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.218108998240125</v>
+        <v>2.151080339856768</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.959451839556135</v>
+        <v>-7.071166270195064</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1820191807003946</v>
+        <v>0.1373334084448228</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.2127614083618</v>
+        <v>-1.324475839000729</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.238499495819517</v>
+        <v>2.171470837436159</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.715686397572691</v>
+        <v>-6.82740082821162</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2753060658408231</v>
+        <v>0.2306202935852513</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.2127614083618</v>
+        <v>-1.324475839000729</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.234280204166567</v>
+        <v>2.16725154578321</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.613923577295396</v>
+        <v>-6.725638007934325</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3181355078717569</v>
+        <v>0.2734497356161851</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.199542339969371</v>
+        <v>-1.3112567706083</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.24433595912204</v>
+        <v>2.177307300738683</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.364073183346322</v>
+        <v>-6.475787613985251</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.410817740435089</v>
+        <v>0.3661319681795172</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.199542339969371</v>
+        <v>-1.3112567706083</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.237078034105743</v>
+        <v>2.170049375722385</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.188181090878889</v>
+        <v>-6.299895521517819</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4847737009427107</v>
+        <v>0.4400879286871389</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.199542339969371</v>
+        <v>-1.3112567706083</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.240677157626391</v>
+        <v>2.173648499243034</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.016734627856425</v>
+        <v>-6.128449058495355</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5666797922062501</v>
+        <v>0.5219940199506778</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.028095876946908</v>
+        <v>-1.139810307585837</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.356872541494423</v>
+        <v>2.289843883111065</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.942445062118086</v>
+        <v>-6.054159492757016</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5954160961178827</v>
+        <v>0.5507303238623105</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9538063112085686</v>
+        <v>-1.065520741847498</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.400466758553724</v>
+        <v>2.333438100170366</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.878809319884152</v>
+        <v>-5.990523750523082</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6255651940657736</v>
+        <v>0.5808794218102018</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8901705689746341</v>
+        <v>-1.001884999613563</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.443343004948401</v>
+        <v>2.376314346565044</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.767382560558231</v>
+        <v>-5.879096991197161</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6513301565799372</v>
+        <v>0.6066443843243654</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8901705689746341</v>
+        <v>-1.001884999613563</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.424537263732197</v>
+        <v>2.35750860534884</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.526952063753371</v>
+        <v>-5.638666494392301</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.749245431926759</v>
+        <v>0.7045596596711867</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6497400721697738</v>
+        <v>-0.7614545028087027</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.570538638439991</v>
+        <v>2.503509980056633</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.454709495582176</v>
+        <v>-5.566423926221106</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.782071773030057</v>
+        <v>0.7373860007744848</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6497400721697738</v>
+        <v>-0.7614545028087027</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.574467952274811</v>
+        <v>2.507439293891453</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.401711173300789</v>
+        <v>-5.513425603939718</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8039496858599522</v>
+        <v>0.7592639136043799</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.594403813167835</v>
+        <v>-0.7061182438067639</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.608348291593314</v>
+        <v>2.541319633209957</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.292906287821062</v>
+        <v>-5.404620718459991</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8444697112718362</v>
+        <v>0.7997839390162644</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.594403813167835</v>
+        <v>-0.7061182438067639</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.605346362813308</v>
+        <v>2.53831770442995</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.126744471433997</v>
+        <v>-5.184599920422981</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9125134748372763</v>
+        <v>0.8893712952416828</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5499816917048862</v>
+        <v>-0.5648983987387837</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.633578672701691</v>
+        <v>2.624628648481353</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.99387678237072</v>
+        <v>-5.051732231359703</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9815547332644106</v>
+        <v>0.9584125536688171</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5499816917048862</v>
+        <v>-0.5648983987387837</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.649472855503515</v>
+        <v>2.640522831283176</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.873703699006221</v>
+        <v>-4.931559147995205</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.030769811050512</v>
+        <v>1.007627631454918</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4298086083403873</v>
+        <v>-0.4447253153742847</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.722722549962516</v>
+        <v>2.713772525742177</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.729031553906483</v>
+        <v>-4.786887002895467</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.098726771651847</v>
+        <v>1.075584592056253</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2851364632406498</v>
+        <v>-0.3000531702745473</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.819613939583798</v>
+        <v>2.810663915363459</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.788906381264176</v>
+        <v>-4.846761830253159</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.060814332110196</v>
+        <v>1.037672152514602</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.345011290598342</v>
+        <v>-0.3599279976322394</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.769726534570609</v>
+        <v>2.76077651035027</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.702106883485166</v>
+        <v>-4.759962332474151</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.117934624544366</v>
+        <v>1.094792444948772</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.345011290598342</v>
+        <v>-0.3599279976322394</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.792127027893175</v>
+        <v>2.783177003672836</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.704576589946972</v>
+        <v>-4.762432038935957</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.117019143333055</v>
+        <v>1.093876963737461</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3474809970601481</v>
+        <v>-0.3623977040940456</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.790717605389503</v>
+        <v>2.781767581169164</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.772946776270983</v>
+        <v>-4.830802225259967</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.100677991278153</v>
+        <v>1.077535811682559</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3382052980239332</v>
+        <v>-0.3531220050578306</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.807289947285934</v>
+        <v>2.798339923065595</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.786734829118029</v>
+        <v>-4.844590278107014</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.085599478771226</v>
+        <v>1.062457299175632</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3382052980239332</v>
+        <v>-0.3531220050578306</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.797726655917825</v>
+        <v>2.788776631697487</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.817727988446735</v>
+        <v>-4.875583437435719</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8979117800801304</v>
+        <v>0.8747696004845367</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3382052980239332</v>
+        <v>-0.3531220050578306</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.622436220958212</v>
+        <v>2.613486196737874</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.642253728654266</v>
+        <v>-4.700109177643251</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9726687159889058</v>
+        <v>0.9495265363933119</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3382052980239332</v>
+        <v>-0.3531220050578306</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.62700345295</v>
+        <v>2.618053428729661</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.753189981295515</v>
+        <v>-4.8110454302845</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9040362436936134</v>
+        <v>0.8808940640980194</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3382052980239332</v>
+        <v>-0.3531220050578306</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.602745481711207</v>
+        <v>2.593795457490868</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.719526435823233</v>
+        <v>-4.777381884812217</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9206330471024318</v>
+        <v>0.8974908675068378</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3045417525516513</v>
+        <v>-0.3194584595855488</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.626074994214481</v>
+        <v>2.617124969994143</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.65967381661951</v>
+        <v>-4.717529265608494</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9547464812160533</v>
+        <v>0.9316043016204594</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3045417525516513</v>
+        <v>-0.3194584595855488</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.636247380646614</v>
+        <v>2.627297356426275</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.573430353593132</v>
+        <v>-4.631285802582116</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9841901370004646</v>
+        <v>0.9610479574048709</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3045417525516513</v>
+        <v>-0.3194584595855488</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.631193651220474</v>
+        <v>2.622243627000135</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.618737172992112</v>
+        <v>-4.676592621981096</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9578431846853983</v>
+        <v>0.9347010050898046</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3453519155608821</v>
+        <v>-0.3602686225947796</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.598483328859461</v>
+        <v>2.589533304639123</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.647770277694413</v>
+        <v>-4.705625726683397</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9467818158375794</v>
+        <v>0.9236396362419856</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3453519155608821</v>
+        <v>-0.3602686225947796</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.599035201892563</v>
+        <v>2.590085177672224</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.554959796243553</v>
+        <v>-4.612815245232538</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.913178700309289</v>
+        <v>0.8900365207136951</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2525414341100228</v>
+        <v>-0.2674581411439202</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.583994182654444</v>
+        <v>2.575044158434106</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.599349265572981</v>
+        <v>-4.657204714561965</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8972963885021188</v>
+        <v>0.8741542089065248</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2969309034394504</v>
+        <v>-0.3118476104733479</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.559233976981388</v>
+        <v>2.55028395276105</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.48667804733673</v>
+        <v>-4.544533496325715</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9374405843083418</v>
+        <v>0.914298404712748</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1842596852032002</v>
+        <v>-0.1991763922370977</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.621912416434861</v>
+        <v>2.612962392214523</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.374301046154057</v>
+        <v>-4.432156495143042</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9878826806120782</v>
+        <v>0.9647405010164845</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1842596852032002</v>
+        <v>-0.1991763922370977</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.627403712265528</v>
+        <v>2.61845368804519</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.40208144405541</v>
+        <v>-4.459936893044395</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9882677232200763</v>
+        <v>0.9651255436244823</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2120400831045533</v>
+        <v>-0.2269567901384508</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.622232675293256</v>
+        <v>2.613282651072917</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.485082725080689</v>
+        <v>-4.542938174069674</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.793422930810618</v>
+        <v>0.770280751215024</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2306109676317271</v>
+        <v>-0.2455276746656245</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.449445864577605</v>
+        <v>2.440495840357266</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.59369680352402</v>
+        <v>-4.651552252513005</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8701269601524912</v>
+        <v>0.8469847805568973</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2306109676317271</v>
+        <v>-0.2455276746656245</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.569595525296811</v>
+        <v>2.560645501076472</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.558287765275877</v>
+        <v>-4.616143214264862</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8988036015540712</v>
+        <v>0.8756614219584775</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2306109676317271</v>
+        <v>-0.2455276746656245</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.584108551399134</v>
+        <v>2.575158527178795</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.519904102717726</v>
+        <v>-4.577759551706711</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9115765079197005</v>
+        <v>0.8884343283241065</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1922273050735759</v>
+        <v>-0.2071440121074734</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.604558190276393</v>
+        <v>2.595608166056055</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.34278777268256</v>
+        <v>-4.400643221671545</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9791520687790687</v>
+        <v>0.956009889183475</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1922273050735759</v>
+        <v>-0.2071440121074734</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.601287219121695</v>
+        <v>2.592337194901356</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.387880017516106</v>
+        <v>-4.445735466505091</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9617985626075636</v>
+        <v>0.9386563830119696</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2541233482429657</v>
+        <v>-0.2690400552768631</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.564832984981974</v>
+        <v>2.555882960761636</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011237</v>
+        <v>3.750729377011239</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.208504596277338</v>
+        <v>-4.266360045266323</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.027335706409485</v>
+        <v>1.004193526813891</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.097346590072247</v>
+        <v>-0.1122632971061445</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.65268601519082</v>
+        <v>2.643735990970481</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.253518809797944</v>
+        <v>-4.311374258786929</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9901374763328326</v>
+        <v>0.9669952967372386</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1276954853868516</v>
+        <v>-0.1426121924207491</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.615284133333647</v>
+        <v>2.606334109113308</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509541</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.520523320070379</v>
+        <v>-4.578378769059364</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8890272345628043</v>
+        <v>0.8658850549672104</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3220585234298002</v>
+        <v>-0.3369752304636977</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.504357872846823</v>
+        <v>2.495407848626485</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.621721101507552</v>
+        <v>-4.679576550496536</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8477520438844366</v>
+        <v>0.8246098642888426</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3904673369751194</v>
+        <v>-0.4053840440090168</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.462516506616133</v>
+        <v>2.453566482395795</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.589245515336779</v>
+        <v>-4.647100964325764</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8583422399070622</v>
+        <v>0.8352000603114682</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3904673369751194</v>
+        <v>-0.4053840440090168</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.46011646817045</v>
+        <v>2.451166443950112</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.570207387629482</v>
+        <v>-4.628062836618467</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8624822101982259</v>
+        <v>0.8393400306026322</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4486509483063139</v>
+        <v>-0.4635676553402114</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.421731020579978</v>
+        <v>2.412780996359639</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.601334018780101</v>
+        <v>-4.659189467769085</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.027613426676659</v>
+        <v>1.004471247081065</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4486509483063139</v>
+        <v>-0.4635676553402114</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.599312889518659</v>
+        <v>2.59036286529832</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067869</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.615200780114018</v>
+        <v>-4.673056229103003</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.022900051129226</v>
+        <v>0.9997578715336317</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4865088650401369</v>
+        <v>-0.5014255720740344</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.577431468464499</v>
+        <v>2.56848144424416</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.570396608574089</v>
+        <v>-4.628252057563073</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.046830250142123</v>
+        <v>1.02368807054653</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4865088650401369</v>
+        <v>-0.5014255720740344</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.583439998861425</v>
+        <v>2.574489974641086</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519912</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.422653638339086</v>
+        <v>-4.480509087328071</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.185080086028147</v>
+        <v>1.161937906432553</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3187015078052537</v>
+        <v>-0.3336182148391512</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.763277060994376</v>
+        <v>2.754327036774038</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181174</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.524668320870307</v>
+        <v>-4.582523769859292</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.147067834547139</v>
+        <v>1.123925654951545</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3187015078052537</v>
+        <v>-0.3336182148391512</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.766070682525857</v>
+        <v>2.757120658305519</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.518515614817523</v>
+        <v>-4.576371063806508</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.150191265359911</v>
+        <v>1.127049085764317</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3125488017524694</v>
+        <v>-0.3274655087863669</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.770424654549186</v>
+        <v>2.761474630328848</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.535324912968025</v>
+        <v>-4.59318036195701</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.14254802283982</v>
+        <v>1.119405843244227</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.329358099902971</v>
+        <v>-0.3442748069368686</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.759419552398995</v>
+        <v>2.750469528178657</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.473026914191903</v>
+        <v>-4.530882363180887</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.23380277614709</v>
+        <v>1.210660596551496</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.329358099902971</v>
+        <v>-0.3442748069368686</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.825755106195816</v>
+        <v>2.816805081975478</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992195</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.271236716526745</v>
+        <v>-4.329092165515729</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.023099727602552</v>
+        <v>0.9999575480069576</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1313399077338167</v>
+        <v>-0.1462566147677142</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.653146893886707</v>
+        <v>2.644196869666368</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.197858619438009</v>
+        <v>-4.255714068426993</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.122741198760221</v>
+        <v>1.099599019164627</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.0579618106450801</v>
+        <v>-0.07287851767897763</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.767463984462124</v>
+        <v>2.758513960241785</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.295599164062983</v>
+        <v>-4.353454613051968</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.098272717026275</v>
+        <v>1.075130537430681</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.07385108877806029</v>
+        <v>-0.08876779581195782</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.772558153698379</v>
+        <v>2.763608129478041</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.471936924185912</v>
+        <v>-4.245052681489962</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.026273593801775</v>
+        <v>1.117027290880155</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2501888489009897</v>
+        <v>0.01963413575004791</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.665291478449293</v>
+        <v>2.827185269239916</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397797</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.395514877753985</v>
+        <v>-4.168630635058035</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.055334030414474</v>
+        <v>1.146087727492854</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2501888489009897</v>
+        <v>0.01963413575004791</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.663783096489222</v>
+        <v>2.825676887279845</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024965</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.351141746115417</v>
+        <v>-4.124257503419466</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.072946150505338</v>
+        <v>1.163699847583718</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2058157172624211</v>
+        <v>0.06400726738861651</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.690269842907799</v>
+        <v>2.852163633698422</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.343187775820645</v>
+        <v>-4.116303533124694</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.076127738623247</v>
+        <v>1.166881435701627</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2058157172624211</v>
+        <v>0.06400726738861651</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.690269842907799</v>
+        <v>2.852163633698422</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.295532045259589</v>
+        <v>-4.068647802563638</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.101571787875474</v>
+        <v>1.192325484953854</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1581599867013654</v>
+        <v>0.1116629979496722</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.725245038272238</v>
+        <v>2.88713882906286</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.167847735465292</v>
+        <v>-3.940963492769342</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.157537885167917</v>
+        <v>1.248291582246297</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.03047567690706898</v>
+        <v>0.2393473077439686</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.80674799752354</v>
+        <v>2.968641788314163</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82883791131455</v>
+        <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.228514325867682</v>
+        <v>-4.001630083171731</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.120025921482834</v>
+        <v>1.210779618561214</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1121739936256027</v>
+        <v>0.1576489910254349</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.744483679968292</v>
+        <v>2.906377470758915</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690025</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.183675924259283</v>
+        <v>-3.956791681563333</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.142058984736821</v>
+        <v>1.232812681815202</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1076305606807332</v>
+        <v>0.1621924239703044</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.751307442345842</v>
+        <v>2.913201233136465</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.284434560016281</v>
+        <v>-4.057550317320331</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.1059164700651</v>
+        <v>1.196670167143481</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1964561294077386</v>
+        <v>0.073366855243299</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.702173040740717</v>
+        <v>2.86406683153134</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163219</v>
+        <v>3.826713779163221</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.240231722930381</v>
+        <v>-4.01334748023443</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.129477207427298</v>
+        <v>1.220230904505678</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1522532923218382</v>
+        <v>0.1175696923291994</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.734574345520095</v>
+        <v>2.896468136310717</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.277210750593824</v>
+        <v>-4.050326507897873</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.113095596831168</v>
+        <v>1.203849293909548</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1152793905305076</v>
+        <v>0.15454359412053</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.755168687064141</v>
+        <v>2.917062477854763</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.297268829458664</v>
+        <v>-4.070384586762714</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.156320130468272</v>
+        <v>1.247073827546652</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1152793905305076</v>
+        <v>0.15454359412053</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.80641645224718</v>
+        <v>2.968310243037803</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.257338156280774</v>
+        <v>-4.030453913584823</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.170733104333681</v>
+        <v>1.261486801412061</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.07534871735261728</v>
+        <v>0.1944742672984203</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.828815560748168</v>
+        <v>2.99070935153879</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232397</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.206306063558246</v>
+        <v>-3.979421820862295</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.186094169660962</v>
+        <v>1.276847866739342</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.02431662463008932</v>
+        <v>0.2455063600209483</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.854383044619954</v>
+        <v>3.016276835410577</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.141081882431041</v>
+        <v>-3.914197639735089</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.229371246204549</v>
+        <v>1.320124943282929</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.0409075564971163</v>
+        <v>0.3107305411481539</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.910704957388983</v>
+        <v>3.072598748179605</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639817</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.103654862359907</v>
+        <v>-3.876770619663956</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.240303026532283</v>
+        <v>1.331056723610663</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.04615909452629796</v>
+        <v>0.3159820791773356</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.909816852505772</v>
+        <v>3.071710643296394</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.845198842749923</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.123766518394615</v>
+        <v>-3.896882275698664</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.23351515644964</v>
+        <v>1.32426885352802</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.05718643952371716</v>
+        <v>0.3270094241747548</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.917690051835464</v>
+        <v>3.079583842626086</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393548</v>
+        <v>3.828690479393549</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.07002170396741</v>
+        <v>-3.843137461271459</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.415570853241733</v>
+        <v>1.506324550320113</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.06724974896417912</v>
+        <v>0.3370727336152167</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.084285808520952</v>
+        <v>3.246179599311574</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714886</v>
+        <v>3.813251854714887</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.046230135361268</v>
+        <v>-3.819345892665317</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.545200389902007</v>
+        <v>1.635954086980387</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.09104131757032141</v>
+        <v>0.360864302221359</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.218673658902454</v>
+        <v>3.380567449693077</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756011</v>
+        <v>3.814259761756013</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.02014605109746</v>
+        <v>-3.793261808401509</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.547341999621389</v>
+        <v>1.638095696699769</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.09104131757032141</v>
+        <v>0.360864302221359</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.210381634916313</v>
+        <v>3.372275425706936</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654185</v>
+        <v>3.803426852654187</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.015811748040412</v>
+        <v>-3.788927505344461</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.547268916427988</v>
+        <v>1.638022613506368</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2426914208895253</v>
+        <v>0.5125144055405628</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.299564892491615</v>
+        <v>3.461458683282238</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717116</v>
+        <v>3.796293177717118</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.006919286647129</v>
+        <v>-3.780035043951178</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.568380306712092</v>
+        <v>1.659134003790473</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2426914208895253</v>
+        <v>0.5125144055405628</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.317119298218406</v>
+        <v>3.479013089009029</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702625</v>
+        <v>3.794453975702627</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.175395403617006</v>
+        <v>-3.948511160921055</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.492844907328725</v>
+        <v>1.583598604407106</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2147435851729446</v>
+        <v>0.4845665698239821</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.292205644193042</v>
+        <v>3.454099434983664</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539967</v>
+        <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.477595874755423</v>
+        <v>-3.250711632059472</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.75323441606122</v>
+        <v>1.843988113139601</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1443955258025338</v>
+        <v>0.4142185104535713</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.231266505758657</v>
+        <v>3.39316029654928</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389897</v>
+        <v>3.784700379389899</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.454874771072271</v>
+        <v>-3.22799052837632</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.752986880031386</v>
+        <v>1.843740577109766</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1443955258025338</v>
+        <v>0.4142185104535713</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.221930528255562</v>
+        <v>3.383824319046184</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534935</v>
+        <v>3.783234730534937</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.453149727782227</v>
+        <v>-3.226265485086276</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.912583023198572</v>
+        <v>2.003336720276953</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1461205690925776</v>
+        <v>0.4159435537436151</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.381871680080757</v>
+        <v>3.54376547087138</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401674</v>
+        <v>3.779962759401675</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.607930734560482</v>
+        <v>-3.19896962538087</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.887748442980917</v>
+        <v>2.051332886652762</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1127528950381015</v>
+        <v>0.4282232865904458</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.398928898141718</v>
+        <v>3.588211133073125</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557222</v>
+        <v>3.769472653557224</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.675191178582399</v>
+        <v>-3.266230069402787</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.857519621361695</v>
+        <v>2.02110406503354</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.04549245101618438</v>
+        <v>0.3609628425685287</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.355247987718113</v>
+        <v>3.54453022264952</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088377</v>
+        <v>3.766702530088379</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.652719644543568</v>
+        <v>-3.243758535363955</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.876514388621969</v>
+        <v>2.040098832293814</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1811979358321556</v>
+        <v>0.4966683273844998</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.446677432252437</v>
+        <v>3.635959667183844</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76808110154137</v>
+        <v>3.768081101541371</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.788672652599884</v>
+        <v>-3.379711543420271</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.006236317544403</v>
+        <v>2.169820761216248</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1811979358321556</v>
+        <v>0.4966683273844998</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.630780564397397</v>
+        <v>3.820062799328804</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743954539471677</v>
+        <v>3.74395453947168</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.811080770404756</v>
+        <v>-3.402119661225143</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.989389765325447</v>
+        <v>2.152974208997292</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1811979358321556</v>
+        <v>0.4966683273844998</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.62289725930039</v>
+        <v>3.812179494231797</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.816337696227745</v>
+        <v>3.569254561742687</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.631821550827503</v>
+        <v>3.481006921517748</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.811080770404756</v>
+        <v>-3.402119661225143</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.989389765325447</v>
+        <v>2.152974208997292</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1811979358321556</v>
+        <v>0.4966683273844998</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.624885347813871</v>
+        <v>3.474070718504116</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240624.xlsx
+++ b/tame_output/ON/bt/strategyON_20240624.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.6%</t>
+          <t>-69.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.4%</t>
+          <t>459.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-501.8%</t>
+          <t>-537.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-50.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>114.0%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.9%</t>
+          <t>-175.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.1%</t>
+          <t>-192.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-174.3%</t>
+          <t>-195.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-98.6%</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539462</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.786778773174088</v>
+        <v>-9.671368523020966</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7802610384467781</v>
+        <v>-0.7340969383855294</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.182505073337614</v>
+        <v>-2.067094823184491</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825303851134037</v>
+        <v>1.89455000122591</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.991036948503952</v>
+        <v>-9.87562669835083</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.856451111460081</v>
+        <v>-0.8102870113988323</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.310144017951603</v>
+        <v>-2.19473376779848</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>1.82347983157616</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.06536992476412</v>
+        <v>-9.949959674610994</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8817017474797111</v>
+        <v>-0.8355376474184619</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.454843541886275</v>
+        <v>-2.339433291733152</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.671896521607918</v>
+        <v>1.741142671699792</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.991900093096667</v>
+        <v>-9.876489842943545</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.83694211331931</v>
+        <v>-0.7907780132580613</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.381373710218827</v>
+        <v>-2.265963460065704</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731350122101808</v>
+        <v>1.800596272193682</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.16702451048321</v>
+        <v>-10.05161426033009</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8924366595264104</v>
+        <v>-0.8462725594651621</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.441087877452248</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.640830692417399</v>
+        <v>1.710076842509273</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.4014766044977</v>
+        <v>-10.28606635434458</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9934366620338024</v>
+        <v>-0.9472725619725542</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.441087877452248</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.633611527515803</v>
+        <v>1.702857677607677</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.50585133552415</v>
+        <v>-10.39044108537102</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.041858745218357</v>
+        <v>-0.9956946451571089</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.660872858631816</v>
+        <v>-2.545462608478693</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.564314498125959</v>
+        <v>1.633560648217833</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.55863749112447</v>
+        <v>-10.44322724097135</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.061857417619931</v>
+        <v>-1.015693317558683</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.756548345214213</v>
+        <v>-2.64113809506109</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.508024996015078</v>
+        <v>1.577271146106951</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.68467428449276</v>
+        <v>-10.56926403433964</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.109578406338132</v>
+        <v>-1.063414306276884</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.615886472251348</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.525869698330037</v>
+        <v>1.595115848421911</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.63265877052395</v>
+        <v>-10.51724852037083</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.084781865064206</v>
+        <v>-1.038617765002958</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.615886472251348</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.529860034016438</v>
+        <v>1.599106184108312</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.77433061224807</v>
+        <v>-10.65892036209495</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.142925828652596</v>
+        <v>-1.096761728591348</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.615886472251348</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.528384807117697</v>
+        <v>1.59763095720957</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.72473976782324</v>
+        <v>-10.60932951767011</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.10803608071779</v>
+        <v>-1.061871980656541</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.681705877979637</v>
+        <v>-2.566295627826514</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.573192723937469</v>
+        <v>1.642438874029343</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.71193237481846</v>
+        <v>-10.59652212466534</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.115964257162564</v>
+        <v>-1.069800157101315</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.730561652988538</v>
+        <v>-2.615151402835415</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.530828125285446</v>
+        <v>1.600074275377319</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.48608722209905</v>
+        <v>-10.37067697194593</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.016047123038591</v>
+        <v>-0.9698830229773425</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.573224727248252</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.565563203673952</v>
+        <v>1.634809353765826</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.36150856576146</v>
+        <v>-10.24609831560834</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9650765159474957</v>
+        <v>-0.9189124158862465</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.573224727248252</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.566702348230011</v>
+        <v>1.635948498321885</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.41440385380575</v>
+        <v>-10.29899360365262</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9836008570031023</v>
+        <v>-0.937436756941854</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.568269381159805</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.572309330045187</v>
+        <v>1.64155548013706</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.34227067851787</v>
+        <v>-10.22686042836474</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9490138826493135</v>
+        <v>-0.9028497825880644</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.568269381159805</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.578043034283823</v>
+        <v>1.647289184375697</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.27090428590822</v>
+        <v>-10.1554940357551</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9302045879993202</v>
+        <v>-0.884040487938071</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.496902988550157</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.611125607455747</v>
+        <v>1.680371757547621</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17744525192299</v>
+        <v>-10.06203500176987</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9027044557181374</v>
+        <v>-0.8565403556568891</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.496902988550157</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.601242126142839</v>
+        <v>1.670488276234713</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.910203451054596</v>
+        <v>-9.794793200901474</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7976422958701521</v>
+        <v>-0.7514781958089034</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.496902988550157</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.599407565643466</v>
+        <v>1.668653715735339</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.812296412378105</v>
+        <v>-9.696886162224983</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7587797953730169</v>
+        <v>-0.7126156953117682</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.544327488842724</v>
+        <v>-2.428917238689601</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.639898700586339</v>
+        <v>1.709144850678212</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.788342871402147</v>
+        <v>-9.672932621249025</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7485298728371399</v>
+        <v>-0.7023657727758912</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.520373947866766</v>
+        <v>-2.404963697713643</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.654939331317407</v>
+        <v>1.724185481409281</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.52428293307935</v>
+        <v>-9.408872682926228</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6561662136697732</v>
+        <v>-0.6100021136085245</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.140903759390847</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.800114978149332</v>
+        <v>1.869361128241206</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.817203309574513</v>
+        <v>-8.701793059421391</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3761213979281393</v>
+        <v>-0.3299572978668905</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.140903759390847</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.797327944489031</v>
+        <v>1.866574094580905</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.777019011208322</v>
+        <v>-8.6616087610552</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3597040546938217</v>
+        <v>-0.313539954632573</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.216129711177779</v>
+        <v>-2.100719461024656</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.821782147396587</v>
+        <v>1.891028297488461</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.613619140268959</v>
+        <v>-8.498208890115837</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2949772850973194</v>
+        <v>-0.2488131850360706</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.052729840238417</v>
+        <v>-1.937319590085294</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919188891180962</v>
+        <v>1.988435041272835</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.37282720891432</v>
+        <v>-8.264727667886238</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1907360837176113</v>
+        <v>-0.1474962673063787</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.811937908883778</v>
+        <v>-1.703838367855695</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.071588478831598</v>
+        <v>2.136448203448447</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.223160817906805</v>
+        <v>-8.115061276878723</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.133761737627565</v>
+        <v>-0.09052192121633196</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.719034417641242</v>
+        <v>-1.610934876613159</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.12443836326416</v>
+        <v>2.189298087881009</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.090885344275918</v>
+        <v>-7.982785803247837</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.0854840614281831</v>
+        <v>-0.04224424501695045</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.586758944010355</v>
+        <v>-1.478659402982273</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.199171134189719</v>
+        <v>2.264030858806568</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.935147011716176</v>
+        <v>-7.827047470688095</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02037366771664928</v>
+        <v>0.02286614869458292</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.431020611450613</v>
+        <v>-1.322921070422531</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.295429194413201</v>
+        <v>2.36028891903005</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.686147213032595</v>
+        <v>-7.578047672004514</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.09213259298044152</v>
+        <v>0.1353724093916742</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.431020611450613</v>
+        <v>-1.322921070422531</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.308335535636859</v>
+        <v>2.373195260253709</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.7917372028057</v>
+        <v>-7.683637661777619</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.07807933252801869</v>
+        <v>-0.03483951611678648</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.536610601223718</v>
+        <v>-1.428511060195636</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.117005612173778</v>
+        <v>2.181865336790628</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.810472104924297</v>
+        <v>-7.702372563896215</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03702895149837104</v>
+        <v>0.006210864912861158</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.542206610883849</v>
+        <v>-1.434107069855767</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.162192348254786</v>
+        <v>2.227052072871635</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.662532063516697</v>
+        <v>-7.554432522488616</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0977318576234989</v>
+        <v>-0.0544920412122667</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.521885694975291</v>
+        <v>-1.413786153947209</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.054505975111753</v>
+        <v>2.119365699728602</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.609562541262709</v>
+        <v>-7.501463000234628</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08525803497538176</v>
+        <v>-0.04201821856414956</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.468916172721303</v>
+        <v>-1.360816631693221</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.077573702210668</v>
+        <v>2.142433426827517</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.566014134492018</v>
+        <v>-7.457914593463937</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07479928436219874</v>
+        <v>-0.03155946795096654</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.468916172721303</v>
+        <v>-1.360816631693221</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.070613090115574</v>
+        <v>2.135472814732424</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.32386574103816</v>
+        <v>-7.215766200010079</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03652242740048761</v>
+        <v>0.07976224381171981</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.468916172721303</v>
+        <v>-1.360816631693221</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.085075444496717</v>
+        <v>2.149935169113567</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.215606603915639</v>
+        <v>-7.107507062887557</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07435820270869131</v>
+        <v>0.1175980191199235</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.468916172721303</v>
+        <v>-1.360816631693221</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.079607564955912</v>
+        <v>2.144467289572762</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.092315469098508</v>
+        <v>-6.984215928070427</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1211727506461204</v>
+        <v>0.1644125670573531</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.345625037904172</v>
+        <v>-1.23752549687609</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.151080339856768</v>
+        <v>2.215940064473617</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.071166270195064</v>
+        <v>-6.963066729166983</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1373334084448228</v>
+        <v>0.1805732248560554</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.324475839000729</v>
+        <v>-1.216376297972647</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.171470837436159</v>
+        <v>2.236330562053008</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.82740082821162</v>
+        <v>-6.719301287183539</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2306202935852513</v>
+        <v>0.2738601099964839</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.324475839000729</v>
+        <v>-1.216376297972647</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.16725154578321</v>
+        <v>2.232111270400059</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.725638007934325</v>
+        <v>-6.617538466906244</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2734497356161851</v>
+        <v>0.3166895520274178</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.3112567706083</v>
+        <v>-1.203157229580218</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.177307300738683</v>
+        <v>2.242167025355532</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.475787613985251</v>
+        <v>-6.367688072957169</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3661319681795172</v>
+        <v>0.4093717845907499</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.3112567706083</v>
+        <v>-1.203157229580218</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.170049375722385</v>
+        <v>2.234909100339234</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.299895521517819</v>
+        <v>-6.191795980489736</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4400879286871389</v>
+        <v>0.4833277450983715</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.3112567706083</v>
+        <v>-1.203157229580218</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.173648499243034</v>
+        <v>2.238508223859883</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.128449058495355</v>
+        <v>-6.020349517467273</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5219940199506778</v>
+        <v>0.5652338363619109</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.139810307585837</v>
+        <v>-1.031710766557755</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.289843883111065</v>
+        <v>2.354703607727915</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.054159492757016</v>
+        <v>-5.946059951728934</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5507303238623105</v>
+        <v>0.5939701402735436</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.065520741847498</v>
+        <v>-0.9574212008194156</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.333438100170366</v>
+        <v>2.398297824787215</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.990523750523082</v>
+        <v>-5.882424209494999</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5808794218102018</v>
+        <v>0.6241192382214344</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.001884999613563</v>
+        <v>-0.8937854585854811</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.376314346565044</v>
+        <v>2.441174071181893</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.879096991197161</v>
+        <v>-5.770997450169079</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6066443843243654</v>
+        <v>0.649884200735598</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.001884999613563</v>
+        <v>-0.8937854585854811</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.35750860534884</v>
+        <v>2.422368329965689</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.638666494392301</v>
+        <v>-5.530566953364219</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7045596596711867</v>
+        <v>0.7477994760824198</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7614545028087027</v>
+        <v>-0.6533549617806208</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.503509980056633</v>
+        <v>2.568369704673482</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.566423926221106</v>
+        <v>-5.458324385193024</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7373860007744848</v>
+        <v>0.7806258171857179</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7614545028087027</v>
+        <v>-0.6533549617806208</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.507439293891453</v>
+        <v>2.572299018508303</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.513425603939718</v>
+        <v>-5.405326062911636</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7592639136043799</v>
+        <v>0.802503730015613</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7061182438067639</v>
+        <v>-0.598018702778682</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.541319633209957</v>
+        <v>2.606179357826806</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.404620718459991</v>
+        <v>-5.296521177431909</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7997839390162644</v>
+        <v>0.8430237554274971</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7061182438067639</v>
+        <v>-0.598018702778682</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.53831770442995</v>
+        <v>2.603177429046799</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.184599920422981</v>
+        <v>-5.076500379394899</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8893712952416828</v>
+        <v>0.9326111116529154</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5648983987387837</v>
+        <v>-0.4567988577107017</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.624628648481353</v>
+        <v>2.689488373098202</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.051732231359703</v>
+        <v>-4.943632690331621</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9584125536688171</v>
+        <v>1.00165237008005</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5648983987387837</v>
+        <v>-0.4567988577107017</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.640522831283176</v>
+        <v>2.705382555900025</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.931559147995205</v>
+        <v>-4.823459606967123</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.007627631454918</v>
+        <v>1.050867447866151</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4447253153742847</v>
+        <v>-0.3366257743462028</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.713772525742177</v>
+        <v>2.778632250359026</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.786887002895467</v>
+        <v>-4.678787461867385</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.075584592056253</v>
+        <v>1.118824408467486</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3000531702745473</v>
+        <v>-0.1919536292464654</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.810663915363459</v>
+        <v>2.875523639980309</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.846761830253159</v>
+        <v>-4.738662289225077</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.037672152514602</v>
+        <v>1.080911968925835</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3599279976322394</v>
+        <v>-0.2518284566041575</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.76077651035027</v>
+        <v>2.825636234967119</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.759962332474151</v>
+        <v>-4.651862791446069</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.094792444948772</v>
+        <v>1.138032261360004</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3599279976322394</v>
+        <v>-0.2518284566041575</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.783177003672836</v>
+        <v>2.848036728289685</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.762432038935957</v>
+        <v>-4.654332497907875</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.093876963737461</v>
+        <v>1.137116780148694</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3623977040940456</v>
+        <v>-0.2542981630659636</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.781767581169164</v>
+        <v>2.846627305786014</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.830802225259967</v>
+        <v>-4.722702684231885</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.077535811682559</v>
+        <v>1.120775628093792</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3531220050578306</v>
+        <v>-0.2450224640297487</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.798339923065595</v>
+        <v>2.863199647682444</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.844590278107014</v>
+        <v>-4.736490737078932</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.062457299175632</v>
+        <v>1.105697115586865</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3531220050578306</v>
+        <v>-0.2450224640297487</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.788776631697487</v>
+        <v>2.853636356314336</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.875583437435719</v>
+        <v>-4.767483896407637</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8747696004845367</v>
+        <v>0.9180094168957695</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3531220050578306</v>
+        <v>-0.2450224640297487</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.613486196737874</v>
+        <v>2.678345921354722</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.700109177643251</v>
+        <v>-4.592009636615169</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9495265363933119</v>
+        <v>0.9927663528045447</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3531220050578306</v>
+        <v>-0.2450224640297487</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.618053428729661</v>
+        <v>2.682913153346511</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.8110454302845</v>
+        <v>-4.702945889256418</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8808940640980194</v>
+        <v>0.9241338805092523</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3531220050578306</v>
+        <v>-0.2450224640297487</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.593795457490868</v>
+        <v>2.658655182107718</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.777381884812217</v>
+        <v>-4.669282343784135</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8974908675068378</v>
+        <v>0.9407306839180707</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3194584595855488</v>
+        <v>-0.2113589185574669</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.617124969994143</v>
+        <v>2.681984694610992</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.717529265608494</v>
+        <v>-4.609429724580412</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9316043016204594</v>
+        <v>0.9748441180316922</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3194584595855488</v>
+        <v>-0.2113589185574669</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.627297356426275</v>
+        <v>2.692157081043125</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.631285802582116</v>
+        <v>-4.523186261554034</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9610479574048709</v>
+        <v>1.004287773816104</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3194584595855488</v>
+        <v>-0.2113589185574669</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.622243627000135</v>
+        <v>2.687103351616985</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.676592621981096</v>
+        <v>-4.568493080953014</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9347010050898046</v>
+        <v>0.9779408215010372</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3602686225947796</v>
+        <v>-0.2521690815666977</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.589533304639123</v>
+        <v>2.654393029255972</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.705625726683397</v>
+        <v>-4.597526185655315</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9236396362419856</v>
+        <v>0.9668794526532185</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3602686225947796</v>
+        <v>-0.2521690815666977</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.590085177672224</v>
+        <v>2.654944902289074</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.612815245232538</v>
+        <v>-4.504715704204456</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8900365207136951</v>
+        <v>0.933276337124928</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2674581411439202</v>
+        <v>-0.1593586001158383</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.575044158434106</v>
+        <v>2.639903883050955</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.657204714561965</v>
+        <v>-4.549105173533883</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8741542089065248</v>
+        <v>0.9173940253177577</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3118476104733479</v>
+        <v>-0.203748069445266</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.55028395276105</v>
+        <v>2.615143677377899</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.544533496325715</v>
+        <v>-4.436433955297633</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.914298404712748</v>
+        <v>0.9575382211239809</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1991763922370977</v>
+        <v>-0.09107685120901576</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.612962392214523</v>
+        <v>2.677822116831372</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.432156495143042</v>
+        <v>-4.32405695411496</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9647405010164845</v>
+        <v>1.007980317427717</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1991763922370977</v>
+        <v>-0.09107685120901576</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.61845368804519</v>
+        <v>2.683313412662039</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.459936893044395</v>
+        <v>-4.351837352016313</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9651255436244823</v>
+        <v>1.008365360035715</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2269567901384508</v>
+        <v>-0.1188572491103688</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.613282651072917</v>
+        <v>2.678142375689767</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.542938174069674</v>
+        <v>-4.434838633041592</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.770280751215024</v>
+        <v>0.8135205676262569</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2455276746656245</v>
+        <v>-0.1374281336375426</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.440495840357266</v>
+        <v>2.505355564974116</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.651552252513005</v>
+        <v>-4.543452711484923</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8469847805568973</v>
+        <v>0.8902245969681302</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2455276746656245</v>
+        <v>-0.1374281336375426</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.560645501076472</v>
+        <v>2.625505225693321</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.616143214264862</v>
+        <v>-4.50804367323678</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8756614219584775</v>
+        <v>0.9189012383697102</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2455276746656245</v>
+        <v>-0.1374281336375426</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.575158527178795</v>
+        <v>2.640018251795644</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.577759551706711</v>
+        <v>-4.469660010678629</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8884343283241065</v>
+        <v>0.9316741447353394</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2071440121074734</v>
+        <v>-0.09904447107939141</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.595608166056055</v>
+        <v>2.660467890672904</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.400643221671545</v>
+        <v>-4.292543680643463</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.956009889183475</v>
+        <v>0.9992497055947078</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2071440121074734</v>
+        <v>-0.09904447107939141</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.592337194901356</v>
+        <v>2.657196919518205</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.445735466505091</v>
+        <v>-4.337635925477008</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9386563830119696</v>
+        <v>0.9818961994232025</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2690400552768631</v>
+        <v>-0.1609405142487812</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.555882960761636</v>
+        <v>2.620742685378485</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.266360045266323</v>
+        <v>-4.158260504238241</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.004193526813891</v>
+        <v>1.047433343225124</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1122632971061445</v>
+        <v>-0.004163756078062519</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.643735990970481</v>
+        <v>2.70859571558733</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.311374258786929</v>
+        <v>-4.203274717758847</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9669952967372386</v>
+        <v>1.010235113148471</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1426121924207491</v>
+        <v>-0.03451265139266713</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.606334109113308</v>
+        <v>2.671193833730158</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.578378769059364</v>
+        <v>-4.470279228031282</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8658850549672104</v>
+        <v>0.9091248713784432</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3369752304636977</v>
+        <v>-0.2288756894356157</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.495407848626485</v>
+        <v>2.560267573243334</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.679576550496536</v>
+        <v>-4.571477009468454</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8246098642888426</v>
+        <v>0.8678496807000755</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4053840440090168</v>
+        <v>-0.2972845029809349</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.453566482395795</v>
+        <v>2.518426207012644</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.647100964325764</v>
+        <v>-4.539001423297682</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8352000603114682</v>
+        <v>0.8784398767227011</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4053840440090168</v>
+        <v>-0.2972845029809349</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.451166443950112</v>
+        <v>2.51602616856696</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.628062836618467</v>
+        <v>-4.519963295590385</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8393400306026322</v>
+        <v>0.882579847013865</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4635676553402114</v>
+        <v>-0.3554681143121294</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.412780996359639</v>
+        <v>2.477640720976489</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.659189467769085</v>
+        <v>-4.551089926741003</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.004471247081065</v>
+        <v>1.047711063492298</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4635676553402114</v>
+        <v>-0.3554681143121294</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.59036286529832</v>
+        <v>2.655222589915169</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.673056229103003</v>
+        <v>-4.564956688074921</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9997578715336317</v>
+        <v>1.042997687944865</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5014255720740344</v>
+        <v>-0.3933260310459524</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.56848144424416</v>
+        <v>2.633341168861009</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.628252057563073</v>
+        <v>-4.520152516534991</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.02368807054653</v>
+        <v>1.066927886957763</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5014255720740344</v>
+        <v>-0.3933260310459524</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.574489974641086</v>
+        <v>2.639349699257935</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.480509087328071</v>
+        <v>-4.372409546299989</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.161937906432553</v>
+        <v>1.205177722843785</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3336182148391512</v>
+        <v>-0.2255186738110692</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.754327036774038</v>
+        <v>2.819186761390887</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.582523769859292</v>
+        <v>-4.47442422883121</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.123925654951545</v>
+        <v>1.167165471362778</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3336182148391512</v>
+        <v>-0.2255186738110692</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.757120658305519</v>
+        <v>2.821980382922368</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.576371063806508</v>
+        <v>-4.468271522778426</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.127049085764317</v>
+        <v>1.17028890217555</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3274655087863669</v>
+        <v>-0.2193659677582849</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.761474630328848</v>
+        <v>2.826334354945697</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.59318036195701</v>
+        <v>-4.485080820928927</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.119405843244227</v>
+        <v>1.16264565965546</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3442748069368686</v>
+        <v>-0.2361752659087866</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.750469528178657</v>
+        <v>2.815329252795506</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.530882363180887</v>
+        <v>-4.422782822152805</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.210660596551496</v>
+        <v>1.253900412962729</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3442748069368686</v>
+        <v>-0.2361752659087866</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.816805081975478</v>
+        <v>2.881664806592327</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.329092165515729</v>
+        <v>-4.220992624487647</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9999575480069576</v>
+        <v>1.04319736441819</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1462566147677142</v>
+        <v>-0.03815707373963217</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.644196869666368</v>
+        <v>2.709056594283218</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.255714068426993</v>
+        <v>-4.147614527398911</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.099599019164627</v>
+        <v>1.14283883557586</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.07287851767897763</v>
+        <v>0.03522102334910437</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.758513960241785</v>
+        <v>2.823373684858635</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.353454613051968</v>
+        <v>-4.245355072023886</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.075130537430681</v>
+        <v>1.118370353841914</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.08876779581195782</v>
+        <v>0.01933174521612419</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.763608129478041</v>
+        <v>2.82846785409489</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.245052681489962</v>
+        <v>-4.421692832146815</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.117027290880155</v>
+        <v>1.046371230617414</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.01963413575004791</v>
+        <v>-0.1570060149068052</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.827185269239916</v>
+        <v>2.721201178845804</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.168630635058035</v>
+        <v>-4.345270785714888</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.146087727492854</v>
+        <v>1.075431667230113</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.01963413575004791</v>
+        <v>-0.1570060149068052</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.825676887279845</v>
+        <v>2.719692796885733</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.124257503419466</v>
+        <v>-4.300897654076319</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.163699847583718</v>
+        <v>1.093043787320977</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.06400726738861651</v>
+        <v>-0.1126328832682366</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.852163633698422</v>
+        <v>2.74617954330431</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.116303533124694</v>
+        <v>-4.292943683781547</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.166881435701627</v>
+        <v>1.096225375438886</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.06400726738861651</v>
+        <v>-0.1126328832682366</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.852163633698422</v>
+        <v>2.74617954330431</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.068647802563638</v>
+        <v>-4.245287953220491</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.192325484953854</v>
+        <v>1.121669424691113</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.1116629979496722</v>
+        <v>-0.06497715270718096</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.88713882906286</v>
+        <v>2.781154738668748</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.940963492769342</v>
+        <v>-4.117603643426195</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.248291582246297</v>
+        <v>1.177635521983556</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.2393473077439686</v>
+        <v>0.06270715708711549</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.968641788314163</v>
+        <v>2.862657697920051</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.001630083171731</v>
+        <v>-4.178270233828584</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.210779618561214</v>
+        <v>1.140123558298473</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.1576489910254349</v>
+        <v>-0.01899115963141818</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.906377470758915</v>
+        <v>2.800393380364803</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.956791681563333</v>
+        <v>-4.133431832220186</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.232812681815202</v>
+        <v>1.162156621552461</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.1621924239703044</v>
+        <v>-0.0144477266865487</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.913201233136465</v>
+        <v>2.807217142742353</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.057550317320331</v>
+        <v>-4.234190467977184</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.196670167143481</v>
+        <v>1.126014106880739</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.073366855243299</v>
+        <v>-0.1032732954135541</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.86406683153134</v>
+        <v>2.758082741137228</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.01334748023443</v>
+        <v>-4.189987630891284</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.220230904505678</v>
+        <v>1.149574844242937</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.1175696923291994</v>
+        <v>-0.05907045832765367</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.896468136310717</v>
+        <v>2.790484045916605</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.050326507897873</v>
+        <v>-4.226966658554726</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.203849293909548</v>
+        <v>1.133193233646807</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.15454359412053</v>
+        <v>-0.02209655653632314</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.917062477854763</v>
+        <v>2.811078387460651</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.070384586762714</v>
+        <v>-4.247024737419567</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.247073827546652</v>
+        <v>1.17641776728391</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.15454359412053</v>
+        <v>-0.02209655653632314</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.968310243037803</v>
+        <v>2.862326152643691</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.030453913584823</v>
+        <v>-4.207094064241677</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.261486801412061</v>
+        <v>1.19083074114932</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.1944742672984203</v>
+        <v>0.0178341166415672</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.99070935153879</v>
+        <v>2.884725261144678</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.979421820862295</v>
+        <v>-4.156061971519149</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.276847866739342</v>
+        <v>1.206191806476601</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.2455063600209483</v>
+        <v>0.06886620936409515</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.016276835410577</v>
+        <v>2.910292745016465</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.914197639735089</v>
+        <v>-4.090837790391944</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.320124943282929</v>
+        <v>1.249468883020188</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.3107305411481539</v>
+        <v>0.1340903904913008</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.072598748179605</v>
+        <v>2.966614657785493</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.876770619663956</v>
+        <v>-4.053410770320809</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.331056723610663</v>
+        <v>1.260400663347922</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.3159820791773356</v>
+        <v>0.1393419285204824</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.071710643296394</v>
+        <v>2.965726552902283</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.896882275698664</v>
+        <v>-4.073522426355518</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.32426885352802</v>
+        <v>1.253612793265279</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.3270094241747548</v>
+        <v>0.1503692735179016</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.079583842626086</v>
+        <v>2.973599752231975</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.843137461271459</v>
+        <v>-4.019777611928313</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.506324550320113</v>
+        <v>1.435668490057372</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.3370727336152167</v>
+        <v>0.1604325829583636</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.246179599311574</v>
+        <v>3.140195508917462</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.819345892665317</v>
+        <v>-3.98990020164127</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.635954086980387</v>
+        <v>1.567732363390006</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.360864302221359</v>
+        <v>0.1903099932454063</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.380567449693077</v>
+        <v>3.278234864307505</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.793261808401509</v>
+        <v>-3.963816117377462</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.638095696699769</v>
+        <v>1.569873973109388</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.360864302221359</v>
+        <v>0.1903099932454063</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.372275425706936</v>
+        <v>3.269942840321364</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.788927505344461</v>
+        <v>-3.959481814320414</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.638022613506368</v>
+        <v>1.569800889915987</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.5125144055405628</v>
+        <v>0.3419600965646102</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.461458683282238</v>
+        <v>3.359126097896666</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.780035043951178</v>
+        <v>-3.950589352927131</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.659134003790473</v>
+        <v>1.590912280200091</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.5125144055405628</v>
+        <v>0.3419600965646102</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.479013089009029</v>
+        <v>3.376680503623458</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.948511160921055</v>
+        <v>-4.119065469897008</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.583598604407106</v>
+        <v>1.515376880816724</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.4845665698239821</v>
+        <v>0.3140122608480295</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.454099434983664</v>
+        <v>3.351766849598093</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.250711632059472</v>
+        <v>-3.421265941035425</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.843988113139601</v>
+        <v>1.77576638954922</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.4142185104535713</v>
+        <v>0.2436642014776187</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.39316029654928</v>
+        <v>3.290827711163709</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.22799052837632</v>
+        <v>-3.398544837352273</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.843740577109766</v>
+        <v>1.775518853519385</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.4142185104535713</v>
+        <v>0.2436642014776187</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.383824319046184</v>
+        <v>3.281491733660613</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.226265485086276</v>
+        <v>-3.396819794062229</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.003336720276953</v>
+        <v>1.935114996686571</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.4159435537436151</v>
+        <v>0.2453892447676625</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.54376547087138</v>
+        <v>3.441432885485808</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.19896962538087</v>
+        <v>-3.551600800840484</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.051332886652762</v>
+        <v>1.910280416468916</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.4282232865904458</v>
+        <v>0.2120215707131864</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.588211133073125</v>
+        <v>3.458490103546769</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557224</v>
+        <v>3.769472653557223</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.266230069402787</v>
+        <v>-3.618861244862401</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.02110406503354</v>
+        <v>1.880051594849694</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.3609628425685287</v>
+        <v>0.1447611266912693</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.54453022264952</v>
+        <v>3.414809193123164</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088379</v>
+        <v>3.766702530088378</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.243758535363955</v>
+        <v>-3.59638971082357</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.040098832293814</v>
+        <v>1.899046362109968</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.4966683273844998</v>
+        <v>0.2804666115072405</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.635959667183844</v>
+        <v>3.506238637657488</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.379711543420271</v>
+        <v>-3.732342718879885</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.169820761216248</v>
+        <v>2.028768291032402</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.4966683273844998</v>
+        <v>0.2804666115072405</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.820062799328804</v>
+        <v>3.690341769802448</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.402119661225143</v>
+        <v>-3.754750836684758</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.152974208997292</v>
+        <v>2.011921738813446</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.4966683273844998</v>
+        <v>0.2804666115072405</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.812179494231797</v>
+        <v>3.682458464705441</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.569254561742687</v>
+        <v>3.83443829754492</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.481006921517748</v>
+        <v>3.645702137741765</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.402119661225143</v>
+        <v>-3.754750836684758</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.152974208997292</v>
+        <v>2.011921738813446</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.4966683273844998</v>
+        <v>0.2804666115072405</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.474070718504116</v>
+        <v>3.638765934728132</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240624.xlsx
+++ b/tame_output/ON/bt/strategyON_20240624.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>49.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.5%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.3%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.2%</t>
+          <t>459.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-537.0%</t>
+          <t>-552.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>120.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-175.0%</t>
+          <t>-181.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-192.9%</t>
+          <t>-175.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-195.9%</t>
+          <t>-214.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>-88.6%</t>
         </is>
       </c>
     </row>
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.671368523020966</v>
+        <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7340969383855294</v>
+        <v>-0.7802610384467781</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.067094823184491</v>
+        <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.89455000122591</v>
+        <v>1.825303851134037</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.87562669835083</v>
+        <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8102870113988323</v>
+        <v>-0.856451111460081</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.19473376779848</v>
+        <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.82347983157616</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.949959674610994</v>
+        <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8355376474184619</v>
+        <v>-0.8817017474797111</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.339433291733152</v>
+        <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.741142671699792</v>
+        <v>1.671896521607918</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.876489842943545</v>
+        <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7907780132580613</v>
+        <v>-0.83694211331931</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.265963460065704</v>
+        <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.800596272193682</v>
+        <v>1.731350122101808</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.05161426033009</v>
+        <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8462725594651621</v>
+        <v>-0.8924366595264104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.441087877452248</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.710076842509273</v>
+        <v>1.640830692417399</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.28606635434458</v>
+        <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9472725619725542</v>
+        <v>-0.9934366620338024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.441087877452248</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.702857677607677</v>
+        <v>1.633611527515803</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.39044108537102</v>
+        <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9956946451571089</v>
+        <v>-1.041858745218357</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.545462608478693</v>
+        <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.633560648217833</v>
+        <v>1.564314498125959</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.44322724097135</v>
+        <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.015693317558683</v>
+        <v>-1.061857417619931</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.64113809506109</v>
+        <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.577271146106951</v>
+        <v>1.508024996015078</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.56926403433964</v>
+        <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.063414306276884</v>
+        <v>-1.109578406338132</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.615886472251348</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.595115848421911</v>
+        <v>1.525869698330037</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.51724852037083</v>
+        <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.038617765002958</v>
+        <v>-1.084781865064206</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.615886472251348</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.599106184108312</v>
+        <v>1.529860034016438</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.65892036209495</v>
+        <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.096761728591348</v>
+        <v>-1.142925828652596</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.615886472251348</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.59763095720957</v>
+        <v>1.528384807117697</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.60932951767011</v>
+        <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.061871980656541</v>
+        <v>-1.10803608071779</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.566295627826514</v>
+        <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.642438874029343</v>
+        <v>1.573192723937469</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.59652212466534</v>
+        <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.069800157101315</v>
+        <v>-1.115964257162564</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.615151402835415</v>
+        <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.600074275377319</v>
+        <v>1.530828125285446</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.37067697194593</v>
+        <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9698830229773425</v>
+        <v>-1.016047123038591</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.573224727248252</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.634809353765826</v>
+        <v>1.565563203673952</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.24609831560834</v>
+        <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9189124158862465</v>
+        <v>-0.9650765159474957</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.573224727248252</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.635948498321885</v>
+        <v>1.566702348230011</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.29899360365262</v>
+        <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.937436756941854</v>
+        <v>-0.9836008570031023</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.568269381159805</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.64155548013706</v>
+        <v>1.572309330045187</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.22686042836474</v>
+        <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9028497825880644</v>
+        <v>-0.9490138826493135</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.568269381159805</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.647289184375697</v>
+        <v>1.578043034283823</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.1554940357551</v>
+        <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.884040487938071</v>
+        <v>-0.9302045879993202</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.496902988550157</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.680371757547621</v>
+        <v>1.611125607455747</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.06203500176987</v>
+        <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8565403556568891</v>
+        <v>-0.9027044557181374</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.496902988550157</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.670488276234713</v>
+        <v>1.601242126142839</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.794793200901474</v>
+        <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7514781958089034</v>
+        <v>-0.7976422958701521</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.496902988550157</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.668653715735339</v>
+        <v>1.599407565643466</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.696886162224983</v>
+        <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7126156953117682</v>
+        <v>-0.7587797953730169</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.428917238689601</v>
+        <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.709144850678212</v>
+        <v>1.639898700586339</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.672932621249025</v>
+        <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7023657727758912</v>
+        <v>-0.7485298728371399</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.404963697713643</v>
+        <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.724185481409281</v>
+        <v>1.654939331317407</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.408872682926228</v>
+        <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6100021136085245</v>
+        <v>-0.6561662136697732</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.140903759390847</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.869361128241206</v>
+        <v>1.800114978149332</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.701793059421391</v>
+        <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3299572978668905</v>
+        <v>-0.3761213979281393</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.140903759390847</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.866574094580905</v>
+        <v>1.797327944489031</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.6616087610552</v>
+        <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.313539954632573</v>
+        <v>-0.3597040546938217</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.100719461024656</v>
+        <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.891028297488461</v>
+        <v>1.821782147396587</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.498208890115837</v>
+        <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2488131850360706</v>
+        <v>-0.2949772850973194</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.937319590085294</v>
+        <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.988435041272835</v>
+        <v>1.919188891180962</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.264727667886238</v>
+        <v>-8.38013791803936</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1474962673063787</v>
+        <v>-0.1936603673676274</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.703838367855695</v>
+        <v>-1.819248618008818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.136448203448447</v>
+        <v>2.067202053356573</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.115061276878723</v>
+        <v>-8.230471527031845</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.09052192121633196</v>
+        <v>-0.1366860212775807</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.610934876613159</v>
+        <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.189298087881009</v>
+        <v>2.120051937789135</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.982785803247837</v>
+        <v>-8.098196053400958</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.04224424501695045</v>
+        <v>-0.08840834507819872</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.478659402982273</v>
+        <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.264030858806568</v>
+        <v>2.194784708714694</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.827047470688095</v>
+        <v>-7.942457720841216</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.02286614869458292</v>
+        <v>-0.02329795136666535</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.322921070422531</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.36028891903005</v>
+        <v>2.291042768938176</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.578047672004514</v>
+        <v>-7.693457922157635</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1353724093916742</v>
+        <v>0.08920830933042589</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.322921070422531</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.373195260253709</v>
+        <v>2.303949110161835</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.683637661777619</v>
+        <v>-7.79904791193074</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03483951611678648</v>
+        <v>-0.08100361617803475</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.428511060195636</v>
+        <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.181865336790628</v>
+        <v>2.112619186698754</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.702372563896215</v>
+        <v>-7.817782814049337</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.006210864912861158</v>
+        <v>-0.03995323514838711</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.434107069855767</v>
+        <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.227052072871635</v>
+        <v>2.157805922779761</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.554432522488616</v>
+        <v>-7.669842772641737</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0544920412122667</v>
+        <v>-0.100656141273515</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.413786153947209</v>
+        <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.119365699728602</v>
+        <v>2.050119549636728</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.501463000234628</v>
+        <v>-7.616873250387749</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.04201821856414956</v>
+        <v>-0.08818231862539783</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.360816631693221</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.142433426827517</v>
+        <v>2.073187276735643</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.457914593463937</v>
+        <v>-7.573324843617058</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.03155946795096654</v>
+        <v>-0.07772356801221481</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.360816631693221</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.135472814732424</v>
+        <v>2.06622666464055</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.215766200010079</v>
+        <v>-7.3311764501632</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.07976224381171981</v>
+        <v>0.03359814375047154</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.360816631693221</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.149935169113567</v>
+        <v>2.080689019021693</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.107507062887557</v>
+        <v>-7.222917313040679</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1175980191199235</v>
+        <v>0.07143391905867524</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.360816631693221</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.144467289572762</v>
+        <v>2.075221139480888</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.984215928070427</v>
+        <v>-7.099626178223548</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1644125670573531</v>
+        <v>0.1182484669961044</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.23752549687609</v>
+        <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.215940064473617</v>
+        <v>2.146693914381743</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.963066729166983</v>
+        <v>-7.078476979320104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1805732248560554</v>
+        <v>0.1344091247948072</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.216376297972647</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.236330562053008</v>
+        <v>2.167084411961135</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.719301287183539</v>
+        <v>-6.83471153733666</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2738601099964839</v>
+        <v>0.2276960099352352</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.216376297972647</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.232111270400059</v>
+        <v>2.162865120308185</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.617538466906244</v>
+        <v>-6.732948717059365</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3166895520274178</v>
+        <v>0.2705254519661695</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.203157229580218</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.242167025355532</v>
+        <v>2.172920875263658</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.367688072957169</v>
+        <v>-6.483098323110291</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4093717845907499</v>
+        <v>0.3632076845295011</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.203157229580218</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.234909100339234</v>
+        <v>2.165662950247361</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.191795980489736</v>
+        <v>-6.307206230642858</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4833277450983715</v>
+        <v>0.4371636450371228</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.203157229580218</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.238508223859883</v>
+        <v>2.169262073768009</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.020349517467273</v>
+        <v>-6.135759767620395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5652338363619109</v>
+        <v>0.5190697363006618</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.031710766557755</v>
+        <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.354703607727915</v>
+        <v>2.285457457636041</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.946059951728934</v>
+        <v>-6.061470201882056</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5939701402735436</v>
+        <v>0.5478060402122944</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9574212008194156</v>
+        <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.398297824787215</v>
+        <v>2.329051674695342</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.882424209494999</v>
+        <v>-5.997834459648121</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6241192382214344</v>
+        <v>0.5779551381601857</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8937854585854811</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.441174071181893</v>
+        <v>2.37192792109002</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.770997450169079</v>
+        <v>-5.886407700322201</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.649884200735598</v>
+        <v>0.6037201006743493</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8937854585854811</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.422368329965689</v>
+        <v>2.353122179873815</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.530566953364219</v>
+        <v>-5.645977203517341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7477994760824198</v>
+        <v>0.7016353760211711</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6533549617806208</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.568369704673482</v>
+        <v>2.499123554581609</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.458324385193024</v>
+        <v>-5.573734635346146</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7806258171857179</v>
+        <v>0.7344617171244692</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6533549617806208</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.572299018508303</v>
+        <v>2.503052868416429</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.405326062911636</v>
+        <v>-5.520736313064758</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.802503730015613</v>
+        <v>0.7563396299543643</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.598018702778682</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.606179357826806</v>
+        <v>2.536933207734932</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.296521177431909</v>
+        <v>-5.411931427585031</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8430237554274971</v>
+        <v>0.7968596553662484</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.598018702778682</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.603177429046799</v>
+        <v>2.533931278954926</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.076500379394899</v>
+        <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9326111116529154</v>
+        <v>0.8864470115916667</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4567988577107017</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.689488373098202</v>
+        <v>2.620242223006328</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.943632690331621</v>
+        <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.00165237008005</v>
+        <v>0.955488270018801</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4567988577107017</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.705382555900025</v>
+        <v>2.636136405808151</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.823459606967123</v>
+        <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.050867447866151</v>
+        <v>1.004703347804903</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3366257743462028</v>
+        <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.778632250359026</v>
+        <v>2.709386100267153</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.678787461867385</v>
+        <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.118824408467486</v>
+        <v>1.072660308406237</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1919536292464654</v>
+        <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.875523639980309</v>
+        <v>2.806277489888435</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.738662289225077</v>
+        <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.080911968925835</v>
+        <v>1.034747868864586</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2518284566041575</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.825636234967119</v>
+        <v>2.756390084875245</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.651862791446069</v>
+        <v>-4.767273041599191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.138032261360004</v>
+        <v>1.091868161298756</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2518284566041575</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.848036728289685</v>
+        <v>2.778790578197811</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.654332497907875</v>
+        <v>-4.769742748060997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.137116780148694</v>
+        <v>1.090952680087445</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2542981630659636</v>
+        <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.846627305786014</v>
+        <v>2.77738115569414</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.722702684231885</v>
+        <v>-4.838112934385007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.120775628093792</v>
+        <v>1.074611528032543</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2450224640297487</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.863199647682444</v>
+        <v>2.793953497590571</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.736490737078932</v>
+        <v>-4.851900987232054</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.105697115586865</v>
+        <v>1.059533015525616</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2450224640297487</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.853636356314336</v>
+        <v>2.784390206222462</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.767483896407637</v>
+        <v>-4.882894146560759</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9180094168957695</v>
+        <v>0.8718453168345206</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2450224640297487</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.678345921354722</v>
+        <v>2.609099771262849</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.592009636615169</v>
+        <v>-4.707419886768291</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9927663528045447</v>
+        <v>0.946602252743296</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2450224640297487</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.682913153346511</v>
+        <v>2.613667003254637</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.702945889256418</v>
+        <v>-4.81835613940954</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9241338805092523</v>
+        <v>0.8779697804480033</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2450224640297487</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.658655182107718</v>
+        <v>2.589409032015844</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.669282343784135</v>
+        <v>-4.784692593937257</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9407306839180707</v>
+        <v>0.8945665838568218</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2113589185574669</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.681984694610992</v>
+        <v>2.612738544519118</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.609429724580412</v>
+        <v>-4.724839974733534</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9748441180316922</v>
+        <v>0.9286800179704435</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2113589185574669</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.692157081043125</v>
+        <v>2.622910930951251</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.523186261554034</v>
+        <v>-4.638596511707156</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.004287773816104</v>
+        <v>0.9581236737548549</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2113589185574669</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.687103351616985</v>
+        <v>2.617857201525111</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.568493080953014</v>
+        <v>-4.683903331106136</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9779408215010372</v>
+        <v>0.9317767214397885</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2521690815666977</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.654393029255972</v>
+        <v>2.585146879164098</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.597526185655315</v>
+        <v>-4.712936435808437</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9668794526532185</v>
+        <v>0.9207153525919696</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2521690815666977</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.654944902289074</v>
+        <v>2.5856987521972</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.504715704204456</v>
+        <v>-4.620125954357578</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.933276337124928</v>
+        <v>0.887112237063679</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1593586001158383</v>
+        <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.639903883050955</v>
+        <v>2.570657732959081</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.549105173533883</v>
+        <v>-4.664515423687005</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9173940253177577</v>
+        <v>0.871229925256509</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.203748069445266</v>
+        <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.615143677377899</v>
+        <v>2.545897527286025</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.436433955297633</v>
+        <v>-4.551844205450755</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9575382211239809</v>
+        <v>0.911374121062732</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.09107685120901576</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.677822116831372</v>
+        <v>2.608575966739498</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.32405695411496</v>
+        <v>-4.439467204268082</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.007980317427717</v>
+        <v>0.9618162173664684</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.09107685120901576</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.683313412662039</v>
+        <v>2.614067262570166</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.351837352016313</v>
+        <v>-4.467247602169435</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.008365360035715</v>
+        <v>0.9622012599744665</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1188572491103688</v>
+        <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.678142375689767</v>
+        <v>2.608896225597893</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.434838633041592</v>
+        <v>-4.550248883194714</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8135205676262569</v>
+        <v>0.7673564675650082</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1374281336375426</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.505355564974116</v>
+        <v>2.436109414882242</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.543452711484923</v>
+        <v>-4.658862961638045</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8902245969681302</v>
+        <v>0.8440604969068812</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1374281336375426</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.625505225693321</v>
+        <v>2.556259075601448</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.50804367323678</v>
+        <v>-4.623453923389902</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9189012383697102</v>
+        <v>0.8727371383084614</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1374281336375426</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.640018251795644</v>
+        <v>2.570772101703771</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.469660010678629</v>
+        <v>-4.585070260831751</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9316741447353394</v>
+        <v>0.8855100446740907</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.09904447107939141</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.660467890672904</v>
+        <v>2.59122174058103</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.292543680643463</v>
+        <v>-4.407953930796585</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9992497055947078</v>
+        <v>0.9530856055334589</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.09904447107939141</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.657196919518205</v>
+        <v>2.587950769426332</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.337635925477008</v>
+        <v>-4.45304617563013</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9818961994232025</v>
+        <v>0.9357320993619538</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1609405142487812</v>
+        <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.620742685378485</v>
+        <v>2.551496535286611</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.158260504238241</v>
+        <v>-4.273670754391363</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.047433343225124</v>
+        <v>1.001269243163875</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.004163756078062519</v>
+        <v>-0.1195740062311853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.70859571558733</v>
+        <v>2.639349565495456</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.203274717758847</v>
+        <v>-4.318684967911969</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.010235113148471</v>
+        <v>0.9640710130872225</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.03451265139266713</v>
+        <v>-0.1499229015457899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.671193833730158</v>
+        <v>2.601947683638284</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.470279228031282</v>
+        <v>-4.585689478184404</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9091248713784432</v>
+        <v>0.8629607713171943</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2288756894356157</v>
+        <v>-0.3442859395887385</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.560267573243334</v>
+        <v>2.49102142315146</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.571477009468454</v>
+        <v>-4.686887259621576</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8678496807000755</v>
+        <v>0.8216855806388268</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2972845029809349</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.518426207012644</v>
+        <v>2.44918005692077</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.539001423297682</v>
+        <v>-4.654411673450804</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8784398767227011</v>
+        <v>0.8322757766614524</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2972845029809349</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.51602616856696</v>
+        <v>2.446780018475087</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.519963295590385</v>
+        <v>-4.635373545743507</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.882579847013865</v>
+        <v>0.8364157469526161</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3554681143121294</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.477640720976489</v>
+        <v>2.408394570884615</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.551089926741003</v>
+        <v>-4.666500176894125</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.047711063492298</v>
+        <v>1.001546963431049</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3554681143121294</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.655222589915169</v>
+        <v>2.585976439823296</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.564956688074921</v>
+        <v>-4.680366938228043</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.042997687944865</v>
+        <v>0.9968335878836156</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3933260310459524</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.633341168861009</v>
+        <v>2.564095018769136</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.520152516534991</v>
+        <v>-4.635562766688113</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.066927886957763</v>
+        <v>1.020763786896514</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3933260310459524</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.639349699257935</v>
+        <v>2.570103549166062</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.372409546299989</v>
+        <v>-4.487819796453111</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.205177722843785</v>
+        <v>1.159013622782537</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2255186738110692</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.819186761390887</v>
+        <v>2.749940611299013</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.47442422883121</v>
+        <v>-4.589834478984332</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.167165471362778</v>
+        <v>1.121001371301529</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2255186738110692</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.821980382922368</v>
+        <v>2.752734232830494</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.468271522778426</v>
+        <v>-4.583681772931548</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.17028890217555</v>
+        <v>1.124124802114301</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2193659677582849</v>
+        <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.826334354945697</v>
+        <v>2.757088204853823</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.485080820928927</v>
+        <v>-4.600491071082049</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.16264565965546</v>
+        <v>1.116481559594211</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2361752659087866</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.815329252795506</v>
+        <v>2.746083102703632</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.422782822152805</v>
+        <v>-4.538193072305927</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.253900412962729</v>
+        <v>1.20773631290148</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2361752659087866</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.881664806592327</v>
+        <v>2.812418656500453</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.220992624487647</v>
+        <v>-4.336402874640769</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.04319736441819</v>
+        <v>0.9970332643569417</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.03815707373963217</v>
+        <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.709056594283218</v>
+        <v>2.639810444191344</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.147614527398911</v>
+        <v>-4.263024777552033</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.14283883557586</v>
+        <v>1.096674735514611</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.03522102334910437</v>
+        <v>-0.08018922680401847</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.823373684858635</v>
+        <v>2.754127534766761</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.245355072023886</v>
+        <v>-4.360765322177008</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.118370353841914</v>
+        <v>1.072206253780665</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.01933174521612419</v>
+        <v>-0.09607850493699865</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.82846785409489</v>
+        <v>2.759221704003016</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.421692832146815</v>
+        <v>-4.537103082299937</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.046371230617414</v>
+        <v>1.000207130556165</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1570060149068052</v>
+        <v>-0.2724162650599281</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.721201178845804</v>
+        <v>2.65195502875393</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397797</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.345270785714888</v>
+        <v>-4.435488478948197</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.075431667230113</v>
+        <v>1.03934458993679</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1570060149068052</v>
+        <v>-0.2724162650599281</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.719692796885733</v>
+        <v>2.650446646793859</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024965</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.300897654076319</v>
+        <v>-4.391115347309628</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.093043787320977</v>
+        <v>1.056956710027653</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1126328832682366</v>
+        <v>-0.2280431334213595</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.74617954330431</v>
+        <v>2.676933393212436</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.292943683781547</v>
+        <v>-4.383161377014856</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.096225375438886</v>
+        <v>1.060138298145562</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1126328832682366</v>
+        <v>-0.2280431334213595</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.74617954330431</v>
+        <v>2.676933393212436</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.245287953220491</v>
+        <v>-4.3355056464538</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.121669424691113</v>
+        <v>1.085582347397789</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.06497715270718096</v>
+        <v>-0.1803874028603038</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.781154738668748</v>
+        <v>2.711908588576875</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.822707244326878</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.117603643426195</v>
+        <v>-4.207821336659504</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.177635521983556</v>
+        <v>1.141548444690232</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.06270715708711549</v>
+        <v>-0.05270309306600734</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.862657697920051</v>
+        <v>2.793411547828177</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.828837911314554</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.178270233828584</v>
+        <v>-4.268487927061893</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.140123558298473</v>
+        <v>1.104036481005149</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.01899115963141818</v>
+        <v>-0.134401409784541</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.800393380364803</v>
+        <v>2.731147230272929</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.133431832220186</v>
+        <v>-4.223649525453494</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.162156621552461</v>
+        <v>1.126069544259137</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.0144477266865487</v>
+        <v>-0.1298579768396715</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.807217142742353</v>
+        <v>2.737970992650479</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.234190467977184</v>
+        <v>-4.324408161210492</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.126014106880739</v>
+        <v>1.089927029587416</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1032732954135541</v>
+        <v>-0.218683545566677</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.758082741137228</v>
+        <v>2.688836591045354</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163221</v>
+        <v>3.826713779163223</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.189987630891284</v>
+        <v>-4.280205324124592</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.149574844242937</v>
+        <v>1.113487766949613</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.05907045832765367</v>
+        <v>-0.1744807084807765</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.790484045916605</v>
+        <v>2.721237895824732</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.226966658554726</v>
+        <v>-4.317184351788034</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.133193233646807</v>
+        <v>1.097106156353484</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.02209655653632314</v>
+        <v>-0.137506806689446</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.811078387460651</v>
+        <v>2.741832237368778</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.247024737419567</v>
+        <v>-4.337242430652875</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.17641776728391</v>
+        <v>1.140330689990587</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.02209655653632314</v>
+        <v>-0.137506806689446</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.862326152643691</v>
+        <v>2.793080002551817</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.207094064241677</v>
+        <v>-4.297311757474985</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.19083074114932</v>
+        <v>1.154743663855996</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.0178341166415672</v>
+        <v>-0.09757613351155564</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.884725261144678</v>
+        <v>2.815479111052805</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232401</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.156061971519149</v>
+        <v>-4.246279664752457</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.206191806476601</v>
+        <v>1.170104729183278</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.06886620936409515</v>
+        <v>-0.04654404078902769</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.910292745016465</v>
+        <v>2.841046594924591</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.090837790391944</v>
+        <v>-4.181055483625252</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.249468883020188</v>
+        <v>1.213381805726865</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1340903904913008</v>
+        <v>0.01868014033817794</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.966614657785493</v>
+        <v>2.89736850769362</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.84009022063982</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.053410770320809</v>
+        <v>-4.143628463554117</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.260400663347922</v>
+        <v>1.224313586054599</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1393419285204824</v>
+        <v>0.0239316783673596</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.965726552902283</v>
+        <v>2.896480402810409</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749923</v>
+        <v>3.845198842749925</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.073522426355518</v>
+        <v>-4.163740119588826</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.253612793265279</v>
+        <v>1.217525715971956</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1503692735179016</v>
+        <v>0.0349590233647788</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.973599752231975</v>
+        <v>2.904353602140101</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393549</v>
+        <v>3.828690479393551</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.019777611928313</v>
+        <v>-4.109995305161621</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.435668490057372</v>
+        <v>1.399581412764048</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1604325829583636</v>
+        <v>0.04502233280524076</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.140195508917462</v>
+        <v>3.070949358825589</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714887</v>
+        <v>3.813251854714889</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.98990020164127</v>
+        <v>-4.086203736555479</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.567732363390006</v>
+        <v>1.529210949424322</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1903099932454063</v>
+        <v>0.06881390141138305</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.278234864307505</v>
+        <v>3.205337209207091</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756013</v>
+        <v>3.814259761756015</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.963816117377462</v>
+        <v>-4.060119652291671</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.569873973109388</v>
+        <v>1.531352559143705</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1903099932454063</v>
+        <v>0.06881390141138305</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.269942840321364</v>
+        <v>3.19704518522095</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654187</v>
+        <v>3.803426852654189</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.959481814320414</v>
+        <v>-4.055785349234623</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.569800889915987</v>
+        <v>1.531279475950303</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3419600965646102</v>
+        <v>0.220464004730587</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.359126097896666</v>
+        <v>3.286228442796252</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717118</v>
+        <v>3.79629317771712</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.950589352927131</v>
+        <v>-4.04689288784134</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.590912280200091</v>
+        <v>1.552390866234408</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3419600965646102</v>
+        <v>0.220464004730587</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.376680503623458</v>
+        <v>3.303782848523043</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702627</v>
+        <v>3.794453975702629</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.119065469897008</v>
+        <v>-4.215369004811217</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.515376880816724</v>
+        <v>1.476855466851041</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3140122608480295</v>
+        <v>0.1925161690140062</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.351766849598093</v>
+        <v>3.278869194497679</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539971</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.421265941035425</v>
+        <v>-3.517569475949634</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.77576638954922</v>
+        <v>1.737244975583536</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2436642014776187</v>
+        <v>0.1221681096435955</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.290827711163709</v>
+        <v>3.217930056063294</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389899</v>
+        <v>3.784700379389901</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.398544837352273</v>
+        <v>-3.494848372266481</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.775518853519385</v>
+        <v>1.736997439553702</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2436642014776187</v>
+        <v>0.1221681096435955</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.281491733660613</v>
+        <v>3.208594078560199</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534937</v>
+        <v>3.783234730534939</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.396819794062229</v>
+        <v>-3.493123328976438</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.935114996686571</v>
+        <v>1.896593582720888</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2453892447676625</v>
+        <v>0.1238931529336392</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.441432885485808</v>
+        <v>3.368535230385394</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401675</v>
+        <v>3.779962759401678</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.551600800840484</v>
+        <v>-3.647904335754693</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.910280416468916</v>
+        <v>1.871759002503232</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.2120215707131864</v>
+        <v>0.09052547887916312</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.458490103546769</v>
+        <v>3.385592448446355</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557223</v>
+        <v>3.769472653557226</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.618861244862401</v>
+        <v>-3.71516477977661</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.880051594849694</v>
+        <v>1.841530180884011</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1447611266912693</v>
+        <v>0.02326503485724601</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.414809193123164</v>
+        <v>3.34191153802275</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088378</v>
+        <v>3.766702530088381</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.59638971082357</v>
+        <v>-3.692693245737778</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.899046362109968</v>
+        <v>1.860524948144285</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2804666115072405</v>
+        <v>0.1589705196732172</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.506238637657488</v>
+        <v>3.433340982557074</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541371</v>
+        <v>3.768081101541373</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.732342718879885</v>
+        <v>-3.828646253794094</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.028768291032402</v>
+        <v>1.990246877066719</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2804666115072405</v>
+        <v>0.1589705196732172</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.690341769802448</v>
+        <v>3.617444114702034</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74395453947168</v>
+        <v>3.743954539471683</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.754750836684758</v>
+        <v>-3.851054371598966</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.011921738813446</v>
+        <v>1.973400324847763</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2804666115072405</v>
+        <v>0.1589705196732172</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.682458464705441</v>
+        <v>3.609560809605027</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.83443829754492</v>
+        <v>3.777557829217475</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.645702137741765</v>
+        <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.754750836684758</v>
+        <v>-3.913004104383411</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.011921738813446</v>
+        <v>1.950674431283622</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.2804666115072405</v>
+        <v>0.09702078688877253</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.638765934728132</v>
+        <v>3.574444969483998</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240624.xlsx
+++ b/tame_output/ON/bt/strategyON_20240624.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>55.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-70.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.1%</t>
+          <t>459.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-552.9%</t>
+          <t>-553.0%</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>120.6%</t>
+          <t>120.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-175.4%</t>
+          <t>-176.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-214.3%</t>
+          <t>-211.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-88.6%</t>
+          <t>-87.1%</t>
         </is>
       </c>
     </row>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397797</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.435488478948197</v>
+        <v>-4.46068103586801</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.03934458993679</v>
+        <v>1.029267567168864</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2724162650599281</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024965</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.391115347309628</v>
+        <v>-4.416307904229441</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.056956710027653</v>
+        <v>1.046879687259728</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2280431334213595</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.383161377014856</v>
+        <v>-4.408353933934669</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.060138298145562</v>
+        <v>1.050061275377637</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2280431334213595</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.3355056464538</v>
+        <v>-4.360698203373613</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.085582347397789</v>
+        <v>1.075505324629864</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1803874028603038</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326878</v>
+        <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.207821336659504</v>
+        <v>-4.233013893579317</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.141548444690232</v>
+        <v>1.131471421922307</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.05270309306600734</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314554</v>
+        <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.268487927061893</v>
+        <v>-4.293680483981706</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.104036481005149</v>
+        <v>1.093959458237224</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.134401409784541</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.223649525453494</v>
+        <v>-4.248842082373308</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.126069544259137</v>
+        <v>1.115992521491212</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1298579768396715</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.324408161210492</v>
+        <v>-4.349600718130306</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.089927029587416</v>
+        <v>1.079850006819491</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.218683545566677</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163223</v>
+        <v>3.826713779163221</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.280205324124592</v>
+        <v>-4.305397881044406</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.113487766949613</v>
+        <v>1.103410744181688</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1744807084807765</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.317184351788034</v>
+        <v>-4.342376908707848</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.097106156353484</v>
+        <v>1.087029133585558</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.137506806689446</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.337242430652875</v>
+        <v>-4.362434987572689</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.140330689990587</v>
+        <v>1.130253667222662</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.137506806689446</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078284</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.297311757474985</v>
+        <v>-4.322504314394799</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.154743663855996</v>
+        <v>1.144666641088071</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.09757613351155564</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232401</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.246279664752457</v>
+        <v>-4.271472221672271</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.170104729183278</v>
+        <v>1.160027706415352</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.04654404078902769</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162116</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.181055483625252</v>
+        <v>-4.206248040545066</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.213381805726865</v>
+        <v>1.203304782958939</v>
       </c>
       <c r="F1988" t="n">
         <v>0.01868014033817794</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84009022063982</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.143628463554117</v>
+        <v>-4.168821020473931</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.224313586054599</v>
+        <v>1.214236563286673</v>
       </c>
       <c r="F1989" t="n">
         <v>0.0239316783673596</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749925</v>
+        <v>3.845198842749923</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.163740119588826</v>
+        <v>-4.18893267650864</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.217525715971956</v>
+        <v>1.20744869320403</v>
       </c>
       <c r="F1990" t="n">
         <v>0.0349590233647788</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393551</v>
+        <v>3.828690479393549</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.109995305161621</v>
+        <v>-4.135187862081435</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.399581412764048</v>
+        <v>1.389504389996123</v>
       </c>
       <c r="F1991" t="n">
         <v>0.04502233280524076</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714889</v>
+        <v>3.813251854714887</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.086203736555479</v>
+        <v>-4.111396293475293</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.529210949424322</v>
+        <v>1.519133926656397</v>
       </c>
       <c r="F1992" t="n">
         <v>0.06881390141138305</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756015</v>
+        <v>3.814259761756013</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.060119652291671</v>
+        <v>-4.085312209211485</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.531352559143705</v>
+        <v>1.521275536375779</v>
       </c>
       <c r="F1993" t="n">
         <v>0.06881390141138305</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654189</v>
+        <v>3.803426852654187</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.055785349234623</v>
+        <v>-4.080977906154437</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.531279475950303</v>
+        <v>1.521202453182378</v>
       </c>
       <c r="F1994" t="n">
         <v>0.220464004730587</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79629317771712</v>
+        <v>3.796293177717118</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.04689288784134</v>
+        <v>-4.072085444761154</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.552390866234408</v>
+        <v>1.542313843466482</v>
       </c>
       <c r="F1995" t="n">
         <v>0.220464004730587</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702629</v>
+        <v>3.794453975702627</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.215369004811217</v>
+        <v>-4.240561561731031</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.476855466851041</v>
+        <v>1.466778444083115</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1925161690140062</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539971</v>
+        <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.517569475949634</v>
+        <v>-3.542762032869448</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.737244975583536</v>
+        <v>1.727167952815611</v>
       </c>
       <c r="F1997" t="n">
         <v>0.1221681096435955</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389901</v>
+        <v>3.784700379389899</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.494848372266481</v>
+        <v>-3.520040929186295</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.736997439553702</v>
+        <v>1.726920416785776</v>
       </c>
       <c r="F1998" t="n">
         <v>0.1221681096435955</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534939</v>
+        <v>3.783234730534937</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.493123328976438</v>
+        <v>-3.518315885896252</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.896593582720888</v>
+        <v>1.886516559952963</v>
       </c>
       <c r="F1999" t="n">
         <v>0.1238931529336392</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401678</v>
+        <v>3.779962759401675</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.647904335754693</v>
+        <v>-3.673096892674507</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.871759002503232</v>
+        <v>1.861681979735307</v>
       </c>
       <c r="F2000" t="n">
         <v>0.09052547887916312</v>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557226</v>
+        <v>3.769472653557224</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.71516477977661</v>
+        <v>-3.649955139788799</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.841530180884011</v>
+        <v>1.867614036879135</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.02326503485724601</v>
+        <v>0.1136672317648708</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.34191153802275</v>
+        <v>3.396152856167325</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088381</v>
+        <v>3.766702530088379</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.692693245737778</v>
+        <v>-3.627483605749968</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.860524948144285</v>
+        <v>1.886608804139409</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1589705196732172</v>
+        <v>0.249372716580842</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.433340982557074</v>
+        <v>3.487582300701649</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541373</v>
+        <v>3.768081101541371</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.828646253794094</v>
+        <v>-3.763436613806284</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.990246877066719</v>
+        <v>2.016330733061843</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1589705196732172</v>
+        <v>0.249372716580842</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.617444114702034</v>
+        <v>3.671685432846609</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743954539471683</v>
+        <v>3.74395453947168</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.851054371598966</v>
+        <v>-3.785844731611156</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.973400324847763</v>
+        <v>1.999484180842887</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1589705196732172</v>
+        <v>0.249372716580842</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.609560809605027</v>
+        <v>3.663802127749602</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.777557829217475</v>
+        <v>3.833765076839247</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.913004104383411</v>
+        <v>-3.913782798766677</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.950674431283622</v>
+        <v>1.950362953530316</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.09702078688877253</v>
+        <v>0.1214346494253207</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.574444969483998</v>
+        <v>3.589093287005927</v>
       </c>
     </row>
   </sheetData>
